--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="G4" t="n">
         <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>3.75</v>
@@ -1160,7 +1160,7 @@
         <v>2.72</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
         <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
         <v>1.54</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q9" t="n">
         <v>1.54</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>2.86</v>
       </c>
       <c r="H11" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I11" t="n">
         <v>3.35</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>4.5</v>
       </c>
       <c r="H12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I12" t="n">
         <v>2.28</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="Q12" t="n">
         <v>2.28</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="G13" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="H13" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="I13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J13" t="n">
         <v>3</v>
       </c>
-      <c r="J13" t="n">
-        <v>2.86</v>
-      </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2924,7 +2924,7 @@
         <v>1.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G4" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="J4" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="Q4" t="n">
         <v>2.14</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>1.47</v>
       </c>
       <c r="G5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H5" t="n">
         <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J5" t="n">
         <v>3.5</v>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q5" t="n">
         <v>1.98</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.48</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="I8" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K9" t="n">
         <v>5.8</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q12" t="n">
         <v>2.28</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -2897,10 +2897,10 @@
         <v>3.9</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I13" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="J13" t="n">
         <v>3</v>
@@ -2921,11 +2921,11 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.94</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH13"/>
+  <dimension ref="A1:BH12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G4" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I4" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="K4" t="n">
         <v>3.5</v>
@@ -1178,7 +1178,7 @@
         <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="J6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1730,13 @@
         <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="H7" t="n">
         <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="J7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="G8" t="n">
         <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="I8" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="J8" t="n">
         <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G9" t="n">
         <v>1.48</v>
@@ -2148,7 +2148,7 @@
         <v>2.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -2509,10 +2509,10 @@
         <v>2.86</v>
       </c>
       <c r="H11" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="I11" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="J11" t="n">
         <v>3.35</v>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q11" t="n">
         <v>1.8</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>4.5</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="I12" t="n">
         <v>2.28</v>
@@ -2730,7 +2730,7 @@
         <v>1.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,201 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Once Caldas</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Atletico Nacional Medellin</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH12"/>
+  <dimension ref="A1:BH17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Trans Narva</t>
+          <t>Henan Songshan Longmen</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Liaoning Tieren FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>2.06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.99</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Thai League 1</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Muangthong Utd</t>
+          <t>Dalian Yingbo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BG Pathumthani United</t>
+          <t>Chongqing Tonglianglong</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.32</v>
+        <v>1.96</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="G4" t="n">
-        <v>3.15</v>
+        <v>310</v>
       </c>
       <c r="H4" t="n">
-        <v>2.98</v>
+        <v>1.44</v>
       </c>
       <c r="I4" t="n">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="J4" t="n">
-        <v>2.76</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S4" t="n">
         <v>2.2</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Shandong Taishan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="X5" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC5" t="n">
         <v>11.5</v>
       </c>
-      <c r="J5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Tianjin Jinmen Tiger FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="G6" t="n">
-        <v>240</v>
+        <v>2.14</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I6" t="n">
-        <v>240</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.07</v>
+        <v>1.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CSA Steaua Bucuresti</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>310</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="I7" t="n">
-        <v>310</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.07</v>
+        <v>2.34</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Thai League 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Middelfart</t>
+          <t>Muangthong Utd</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aarhus Fremad</t>
+          <t>BG Pathumthani United</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.3</v>
+        <v>2.32</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="n">
-        <v>1.44</v>
+        <v>2.88</v>
       </c>
       <c r="I8" t="n">
-        <v>1.58</v>
+        <v>3.65</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Al-Masry</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.42</v>
+        <v>2.54</v>
       </c>
       <c r="G9" t="n">
-        <v>1.48</v>
+        <v>2.84</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>8.199999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="J9" t="n">
-        <v>5.2</v>
+        <v>2.76</v>
       </c>
       <c r="K9" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HB Koge</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>B93 Copenhagen</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="G10" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82</v>
+        <v>5.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.48</v>
+        <v>1.71</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.48</v>
+        <v>1.98</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AaB</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hobro</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.86</v>
+        <v>240</v>
       </c>
       <c r="H11" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>3.05</v>
+        <v>240</v>
       </c>
       <c r="J11" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.04</v>
+        <v>1.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,201 +2666,1171 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Romanian Liga II</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Chindia Targoviste</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CSA Steaua Bucuresti</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>310</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I12" t="n">
+        <v>310</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K12" t="n">
+        <v>950</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:14:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Middelfart</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aarhus Fremad</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:14:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:14:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HB Koge</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>B93 Copenhagen</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:14:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AaB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Hobro</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:14:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Egyptian Premier</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Zamalek</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Al Ahly Cairo</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F17" t="n">
         <v>3.9</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G17" t="n">
         <v>4.5</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H17" t="n">
         <v>2.06</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I17" t="n">
         <v>2.28</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J17" t="n">
         <v>3.15</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K17" t="n">
         <v>3.5</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>1.65</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q17" t="n">
         <v>2.3</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2026-04-29 07:03:32</t>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH17"/>
+  <dimension ref="A1:BH48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -844,16 +844,16 @@
         <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
         <v>28</v>
       </c>
       <c r="AK2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
         <v>120</v>
@@ -865,19 +865,19 @@
         <v>65</v>
       </c>
       <c r="AP2" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>22</v>
+        <v>3.85</v>
       </c>
       <c r="AS2" t="n">
         <v>4.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
@@ -889,16 +889,16 @@
         <v>4</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
@@ -907,7 +907,7 @@
         <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BE2" t="n">
         <v>4.1</v>
@@ -916,11 +916,11 @@
         <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
@@ -963,13 +963,13 @@
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
         <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -993,7 +993,7 @@
         <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U3" t="n">
         <v>1.98</v>
@@ -1080,7 +1080,7 @@
         <v>15.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.1</v>
+        <v>44</v>
       </c>
       <c r="AX3" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
         <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.2</v>
+        <v>55</v>
       </c>
       <c r="BB3" t="n">
         <v>20</v>
@@ -1101,7 +1101,7 @@
         <v>18.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>32</v>
+        <v>4.9</v>
       </c>
       <c r="BE3" t="n">
         <v>5.4</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Trans Narva</t>
+          <t>Eskilsminne</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Angelholms</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,22 +1169,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.04</v>
+        <v>1.07</v>
       </c>
       <c r="O4" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>1.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.06</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>1.19</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1193,10 +1193,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Shandong Taishan</t>
+          <t>Hassleholms IF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>1.58</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>5.2</v>
+        <v>1.07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>2.42</v>
+        <v>1.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>1.57</v>
+        <v>1.06</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="T5" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,60 +1519,60 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tianjin Jinmen Tiger FC</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.96</v>
+        <v>5.1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.14</v>
+        <v>21</v>
       </c>
       <c r="H6" t="n">
-        <v>3.85</v>
+        <v>1.43</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>1.63</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="O6" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="P6" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1581,55 +1581,55 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>2.58</v>
       </c>
       <c r="W6" t="n">
-        <v>1.87</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.84</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.24</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.72</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.38</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.56</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.72</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.58</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.58</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.68</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.84</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shandong Taishan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="H7" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="Q7" t="n">
         <v>1.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Thai League 1</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,33 +1907,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Muangthong Utd</t>
+          <t>Tianjin Jinmen Tiger FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BG Pathumthani United</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.32</v>
+        <v>1.96</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8</v>
+        <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="I8" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
         <v>4</v>
@@ -1942,156 +1942,156 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>1.99</v>
+        <v>3.65</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T8" t="n">
         <v>1.79</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.84</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="I9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Thai League 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Muangthong Utd</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>BG Pathumthani United</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.47</v>
+        <v>2.32</v>
       </c>
       <c r="G10" t="n">
-        <v>1.68</v>
+        <v>2.68</v>
       </c>
       <c r="H10" t="n">
-        <v>5.2</v>
+        <v>2.88</v>
       </c>
       <c r="I10" t="n">
-        <v>11.5</v>
+        <v>3.65</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>1.71</v>
+        <v>1.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>Sudtirol</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="G11" t="n">
-        <v>240</v>
+        <v>2.28</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="I11" t="n">
-        <v>240</v>
+        <v>4.2</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.07</v>
+        <v>1.86</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CSA Steaua Bucuresti</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="G12" t="n">
-        <v>310</v>
+        <v>3.65</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="I12" t="n">
-        <v>310</v>
+        <v>2.36</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>1.07</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Middelfart</t>
+          <t>SSD Bari</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aarhus Fremad</t>
+          <t>Entella</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>2.94</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>3.35</v>
       </c>
       <c r="H13" t="n">
-        <v>1.44</v>
+        <v>2.52</v>
       </c>
       <c r="I13" t="n">
-        <v>1.53</v>
+        <v>2.84</v>
       </c>
       <c r="J13" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="K13" t="n">
-        <v>5.9</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P13" t="n">
-        <v>2.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="I14" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X14" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS14" t="n">
         <v>5.2</v>
       </c>
-      <c r="K14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HB Koge</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B93 Copenhagen</t>
+          <t>AC Monza</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U15" t="n">
         <v>2</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="I15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,378 +3459,6392 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AaB</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hobro</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="G16" t="n">
-        <v>2.86</v>
+        <v>5.1</v>
       </c>
       <c r="H16" t="n">
-        <v>2.64</v>
+        <v>1.78</v>
       </c>
       <c r="I16" t="n">
-        <v>2.94</v>
+        <v>1.86</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Italian Serie B</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Italian Serie B</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Pescara</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X18" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Italian Serie B</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Carrarese</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Cesena</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X19" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Italian Serie B</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Calcio Avellino SSD</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I20" t="n">
+        <v>110</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="K20" t="n">
+        <v>950</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Odds BK</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Raufoss</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Turkish Super League</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Rizespor</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Konyaspor</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Turkish 1 Lig</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Boluspor</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Serik Belediyespor</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G23" t="n">
+        <v>240</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I23" t="n">
+        <v>240</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K23" t="n">
+        <v>950</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sogndal</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Hodd</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Asane</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Lyn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Stabaek</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Kongsvinger</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Egersund</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Grindavik</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Njardvik</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Estonian Premier League</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Paide Linnameeskond</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Tammeka Tartu</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Egyptian Premier</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pyramids</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ENPPI</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X30" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Ceramica Cleopatra</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Al-Masry</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X31" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sandnes Ulf</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>11:15:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FC Andorra</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Romanian Liga II</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Chindia Targoviste</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CSA Steaua Bucuresti</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G34" t="n">
+        <v>310</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I34" t="n">
+        <v>310</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K34" t="n">
+        <v>950</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H35" t="n">
+        <v>7</v>
+      </c>
+      <c r="I35" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Middelfart</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aarhus Fremad</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>11</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Afturelding</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Volsungur</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Deportivo</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I38" t="n">
+        <v>6</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HB Koge</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>B93 Copenhagen</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AaB</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Hobro</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>Zamalek</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Al Ahly Cairo</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F41" t="n">
         <v>3.9</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G41" t="n">
         <v>4.5</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H41" t="n">
         <v>2.06</v>
       </c>
-      <c r="I17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="I41" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J41" t="n">
         <v>3.15</v>
       </c>
-      <c r="K17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="K41" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
         <v>1.65</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q41" t="n">
         <v>2.3</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>2026-04-29 09:14:08</t>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>IFK Stocksund</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Vasalunds IF</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Turkish 1 Lig</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Manisa FK</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Sakaryaspor</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G43" t="n">
+        <v>240</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I43" t="n">
+        <v>240</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K43" t="n">
+        <v>950</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Turkish Super League</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Gaziantep FK</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G44" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J44" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Ranheim IL</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I46" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH46" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HK Kopavogur</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aegir</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH47" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Grotta</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Leiknir R</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH48" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
@@ -760,19 +760,19 @@
         <v>3.25</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="J2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -784,19 +784,19 @@
         <v>2.22</v>
       </c>
       <c r="O2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P2" t="n">
         <v>2.22</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R2" t="n">
         <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -805,7 +805,7 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="W2" t="n">
         <v>1.37</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G3" t="n">
         <v>2.06</v>
@@ -981,28 +981,28 @@
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R3" t="n">
         <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
         <v>1.76</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V3" t="n">
         <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="X3" t="n">
         <v>19</v>
@@ -1053,7 +1053,7 @@
         <v>120</v>
       </c>
       <c r="AN3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO3" t="n">
         <v>65</v>
@@ -1065,10 +1065,10 @@
         <v>14</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT3" t="n">
         <v>8.6</v>
@@ -1080,7 +1080,7 @@
         <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX3" t="n">
         <v>11</v>
@@ -1101,20 +1101,20 @@
         <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H4" t="n">
         <v>4</v>
@@ -1169,10 +1169,10 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
         <v>1.81</v>
@@ -1190,13 +1190,13 @@
         <v>1.85</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W4" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X4" t="n">
         <v>13.5</v>
@@ -1214,7 +1214,7 @@
         <v>9</v>
       </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
         <v>17</v>
@@ -1247,7 +1247,7 @@
         <v>120</v>
       </c>
       <c r="AN4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO4" t="n">
         <v>65</v>
@@ -1256,7 +1256,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
         <v>24</v>
@@ -1265,7 +1265,7 @@
         <v>36</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU4" t="n">
         <v>7</v>
@@ -1280,13 +1280,13 @@
         <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BB4" t="n">
         <v>20</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G8" t="n">
         <v>1.58</v>
@@ -1930,7 +1930,7 @@
         <v>6.2</v>
       </c>
       <c r="I8" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
         <v>4.7</v>
@@ -1951,22 +1951,22 @@
         <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q8" t="n">
         <v>1.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V8" t="n">
         <v>1.16</v>
@@ -2077,14 +2077,14 @@
         <v>5.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BG8" t="n">
         <v>5.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H9" t="n">
         <v>3.85</v>
@@ -2130,7 +2130,7 @@
         <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2145,7 +2145,7 @@
         <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q9" t="n">
         <v>1.94</v>
@@ -2166,13 +2166,13 @@
         <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X9" t="n">
         <v>17.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Z9" t="n">
         <v>38</v>
@@ -2187,13 +2187,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
         <v>65</v>
       </c>
       <c r="AF9" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG9" t="n">
         <v>12.5</v>
@@ -2229,10 +2229,10 @@
         <v>11</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AT9" t="n">
         <v>8</v>
@@ -2244,7 +2244,7 @@
         <v>12.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX9" t="n">
         <v>10.5</v>
@@ -2256,7 +2256,7 @@
         <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BB9" t="n">
         <v>20</v>
@@ -2265,20 +2265,20 @@
         <v>18</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF9" t="n">
         <v>11</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>2.2</v>
       </c>
       <c r="H10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I10" t="n">
         <v>3.8</v>
@@ -2324,7 +2324,7 @@
         <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.27</v>
@@ -2342,13 +2342,13 @@
         <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R10" t="n">
         <v>1.54</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T10" t="n">
         <v>1.58</v>
@@ -2357,7 +2357,7 @@
         <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
         <v>1.83</v>
@@ -2369,7 +2369,7 @@
         <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA10" t="n">
         <v>65</v>
@@ -2387,7 +2387,7 @@
         <v>38</v>
       </c>
       <c r="AF10" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG10" t="n">
         <v>12</v>
@@ -2411,7 +2411,7 @@
         <v>75</v>
       </c>
       <c r="AN10" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AO10" t="n">
         <v>27</v>
@@ -2420,7 +2420,7 @@
         <v>19</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AR10" t="n">
         <v>21</v>
@@ -2438,7 +2438,7 @@
         <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
@@ -2450,10 +2450,10 @@
         <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BC10" t="n">
         <v>17</v>
@@ -2462,7 +2462,7 @@
         <v>21</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BF10" t="n">
         <v>8.4</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I11" t="n">
         <v>3.65</v>
@@ -2524,10 +2524,10 @@
         <v>1.31</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
         <v>1.27</v>
@@ -2536,13 +2536,13 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R11" t="n">
         <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
         <v>1.66</v>
@@ -2551,10 +2551,10 @@
         <v>2.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X11" t="n">
         <v>20</v>
@@ -2602,7 +2602,7 @@
         <v>44</v>
       </c>
       <c r="AM11" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN11" t="n">
         <v>21</v>
@@ -2662,11 +2662,11 @@
         <v>12.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G12" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H12" t="n">
         <v>3.9</v>
       </c>
       <c r="I12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K12" t="n">
         <v>3.6</v>
@@ -2721,19 +2721,19 @@
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
         <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="Q12" t="n">
         <v>2.26</v>
       </c>
       <c r="R12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
         <v>4.1</v>
@@ -2742,13 +2742,13 @@
         <v>1.91</v>
       </c>
       <c r="U12" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X12" t="n">
         <v>13.5</v>
@@ -2823,7 +2823,7 @@
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AW12" t="n">
         <v>8</v>
@@ -2844,7 +2844,7 @@
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="BD12" t="n">
         <v>7.8</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
         <v>1.26</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q13" t="n">
         <v>1.8</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
         <v>1.38</v>
@@ -3133,7 +3133,7 @@
         <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W14" t="n">
         <v>1.46</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G15" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="H15" t="n">
         <v>5.5</v>
@@ -3291,7 +3291,7 @@
         <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
         <v>4.6</v>
@@ -3318,7 +3318,7 @@
         <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
         <v>1.92</v>
@@ -3327,10 +3327,10 @@
         <v>2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="X15" t="n">
         <v>19</v>
@@ -3354,7 +3354,7 @@
         <v>27</v>
       </c>
       <c r="AE15" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF15" t="n">
         <v>11</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="G16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H16" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="I16" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
@@ -3506,7 +3506,7 @@
         <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R16" t="n">
         <v>1.36</v>
@@ -3515,7 +3515,7 @@
         <v>3.45</v>
       </c>
       <c r="T16" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U16" t="n">
         <v>2</v>
@@ -3536,13 +3536,13 @@
         <v>11</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AB16" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
         <v>9.800000000000001</v>
@@ -3551,10 +3551,10 @@
         <v>19</v>
       </c>
       <c r="AF16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH16" t="n">
         <v>21</v>
@@ -3578,7 +3578,7 @@
         <v>80</v>
       </c>
       <c r="AO16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP16" t="n">
         <v>12.5</v>
@@ -3608,35 +3608,35 @@
         <v>34</v>
       </c>
       <c r="AY16" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ16" t="n">
         <v>17.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BB16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC16" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BF16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG16" t="n">
         <v>10.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
         <v>180</v>
       </c>
       <c r="AB17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC17" t="n">
         <v>10.5</v>
@@ -3781,10 +3781,10 @@
         <v>19.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT17" t="n">
         <v>8.4</v>
@@ -3796,7 +3796,7 @@
         <v>19</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX17" t="n">
         <v>9.199999999999999</v>
@@ -3808,7 +3808,7 @@
         <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB17" t="n">
         <v>13.5</v>
@@ -3817,20 +3817,20 @@
         <v>13.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF17" t="n">
         <v>6.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
         <v>55</v>
       </c>
       <c r="AO18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP18" t="n">
         <v>16.5</v>
@@ -3990,22 +3990,22 @@
         <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AX18" t="n">
         <v>27</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AZ18" t="n">
         <v>15</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC18" t="n">
         <v>38</v>
@@ -4017,14 +4017,14 @@
         <v>4.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="BG18" t="n">
         <v>7.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G19" t="n">
         <v>2.92</v>
@@ -4070,7 +4070,7 @@
         <v>3.75</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.33</v>
@@ -4079,19 +4079,19 @@
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O19" t="n">
         <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q19" t="n">
         <v>1.68</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
         <v>2.72</v>
@@ -4100,7 +4100,7 @@
         <v>1.61</v>
       </c>
       <c r="U19" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="V19" t="n">
         <v>1.59</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
         <v>4.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P20" t="n">
         <v>2.18</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
         <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="R23" t="n">
         <v>1.43</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -5228,10 +5228,10 @@
         <v>3.35</v>
       </c>
       <c r="I25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="K25" t="n">
         <v>4.2</v>
@@ -5258,7 +5258,7 @@
         <v>1.46</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="T25" t="n">
         <v>1.64</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -5607,19 +5607,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G27" t="n">
         <v>2.94</v>
       </c>
       <c r="H27" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I27" t="n">
         <v>2.92</v>
       </c>
       <c r="J27" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K27" t="n">
         <v>4.6</v>
@@ -5631,19 +5631,19 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O27" t="n">
         <v>1.14</v>
       </c>
       <c r="P27" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q27" t="n">
         <v>1.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S27" t="n">
         <v>2.02</v>
@@ -5655,7 +5655,7 @@
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W27" t="n">
         <v>1.51</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         <v>2.1</v>
       </c>
       <c r="G28" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="H28" t="n">
         <v>3.15</v>
@@ -5840,7 +5840,7 @@
         <v>1.63</v>
       </c>
       <c r="S28" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="T28" t="n">
         <v>1.44</v>
@@ -5852,7 +5852,7 @@
         <v>1.33</v>
       </c>
       <c r="W28" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X28" t="n">
         <v>32</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -6004,10 +6004,10 @@
         <v>1.89</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="J29" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K29" t="n">
         <v>5.4</v>
@@ -6043,7 +6043,7 @@
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="W29" t="n">
         <v>1.3</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>1.45</v>
       </c>
       <c r="G30" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="H30" t="n">
         <v>5.1</v>
@@ -6201,7 +6201,7 @@
         <v>7.6</v>
       </c>
       <c r="J30" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="K30" t="n">
         <v>6.2</v>
@@ -6225,10 +6225,10 @@
         <v>1.38</v>
       </c>
       <c r="R30" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="S30" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="T30" t="n">
         <v>1.55</v>
@@ -6240,7 +6240,7 @@
         <v>1.15</v>
       </c>
       <c r="W30" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X30" t="n">
         <v>40</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -6580,13 +6580,13 @@
         <v>2.54</v>
       </c>
       <c r="G32" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="H32" t="n">
         <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="J32" t="n">
         <v>2.74</v>
@@ -6616,7 +6616,7 @@
         <v>1.26</v>
       </c>
       <c r="S32" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="T32" t="n">
         <v>1.73</v>
@@ -6625,10 +6625,10 @@
         <v>1.81</v>
       </c>
       <c r="V32" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W32" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="X32" t="n">
         <v>13.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>1.62</v>
       </c>
       <c r="G33" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H33" t="n">
         <v>4.6</v>
@@ -6795,7 +6795,7 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O33" t="n">
         <v>1.15</v>
@@ -6813,7 +6813,7 @@
         <v>2.1</v>
       </c>
       <c r="T33" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="U33" t="n">
         <v>2.46</v>
@@ -6822,10 +6822,10 @@
         <v>1.19</v>
       </c>
       <c r="W33" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X33" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y33" t="n">
         <v>34</v>
@@ -6873,7 +6873,7 @@
         <v>75</v>
       </c>
       <c r="AN33" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO33" t="n">
         <v>46</v>
@@ -6909,7 +6909,7 @@
         <v>8</v>
       </c>
       <c r="AZ33" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA33" t="n">
         <v>1.01</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="G40" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="H40" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I40" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J40" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K40" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L40" t="n">
         <v>1.23</v>
@@ -8174,7 +8174,7 @@
         <v>1.77</v>
       </c>
       <c r="U40" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V40" t="n">
         <v>1.11</v>
@@ -8186,25 +8186,25 @@
         <v>34</v>
       </c>
       <c r="Y40" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z40" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA40" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB40" t="n">
         <v>14</v>
       </c>
       <c r="AC40" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD40" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE40" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF40" t="n">
         <v>13</v>
@@ -8213,10 +8213,10 @@
         <v>12.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI40" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ40" t="n">
         <v>16</v>
@@ -8228,7 +8228,7 @@
         <v>36</v>
       </c>
       <c r="AM40" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN40" t="n">
         <v>6.2</v>
@@ -8237,16 +8237,16 @@
         <v>110</v>
       </c>
       <c r="AP40" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AQ40" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT40" t="n">
         <v>10</v>
@@ -8255,10 +8255,10 @@
         <v>11</v>
       </c>
       <c r="AV40" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX40" t="n">
         <v>9.199999999999999</v>
@@ -8267,10 +8267,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ40" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB40" t="n">
         <v>11.5</v>
@@ -8279,20 +8279,20 @@
         <v>12.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF40" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
         <v>2.98</v>
       </c>
       <c r="I42" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J42" t="n">
         <v>2.94</v>
@@ -8565,7 +8565,7 @@
         <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W42" t="n">
         <v>1.52</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -8908,10 +8908,10 @@
         <v>6.2</v>
       </c>
       <c r="G44" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="H44" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="I44" t="n">
         <v>1.49</v>
@@ -8920,7 +8920,7 @@
         <v>4.4</v>
       </c>
       <c r="K44" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -8938,13 +8938,13 @@
         <v>2.34</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="R44" t="n">
         <v>1.25</v>
       </c>
       <c r="S44" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -10072,19 +10072,19 @@
         <v>1.49</v>
       </c>
       <c r="G50" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H50" t="n">
         <v>5.7</v>
       </c>
       <c r="I50" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J50" t="n">
         <v>4.8</v>
       </c>
       <c r="K50" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
@@ -10117,16 +10117,16 @@
         <v>2.18</v>
       </c>
       <c r="V50" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W50" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X50" t="n">
         <v>32</v>
       </c>
       <c r="Y50" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="Z50" t="n">
         <v>80</v>
@@ -10177,16 +10177,16 @@
         <v>100</v>
       </c>
       <c r="AP50" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="AQ50" t="n">
         <v>12.5</v>
       </c>
       <c r="AR50" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS50" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="AT50" t="n">
         <v>9.4</v>
@@ -10195,25 +10195,25 @@
         <v>8</v>
       </c>
       <c r="AV50" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW50" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX50" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AY50" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AZ50" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BA50" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB50" t="n">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="BC50" t="n">
         <v>12</v>
@@ -10222,7 +10222,7 @@
         <v>6.8</v>
       </c>
       <c r="BE50" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF50" t="n">
         <v>3.7</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10269,7 @@
         <v>2.4</v>
       </c>
       <c r="H51" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I51" t="n">
         <v>3.15</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -10505,7 +10505,7 @@
         <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W52" t="n">
         <v>1.54</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -10675,7 +10675,7 @@
         <v>1.01</v>
       </c>
       <c r="N53" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O53" t="n">
         <v>1.01</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -10869,13 +10869,13 @@
         <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="O54" t="n">
         <v>1.22</v>
       </c>
       <c r="P54" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q54" t="n">
         <v>1.22</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -11063,7 +11063,7 @@
         <v>1.06</v>
       </c>
       <c r="N55" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="O55" t="n">
         <v>1.27</v>
@@ -11078,7 +11078,7 @@
         <v>1.39</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="T55" t="n">
         <v>1.46</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -11257,13 +11257,13 @@
         <v>1.01</v>
       </c>
       <c r="N56" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O56" t="n">
         <v>1.01</v>
       </c>
       <c r="P56" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Q56" t="n">
         <v>1.27</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -12009,22 +12009,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="G60" t="n">
         <v>2.1</v>
       </c>
       <c r="H60" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="I60" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="J60" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="K60" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="L60" t="n">
         <v>1.01</v>
@@ -12057,7 +12057,7 @@
         <v>1.01</v>
       </c>
       <c r="V60" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="W60" t="n">
         <v>1.9</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="G62" t="n">
         <v>2.48</v>
@@ -12406,7 +12406,7 @@
         <v>3.55</v>
       </c>
       <c r="I62" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J62" t="n">
         <v>3.1</v>
@@ -12421,13 +12421,13 @@
         <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="O62" t="n">
         <v>1.4</v>
       </c>
       <c r="P62" t="n">
-        <v>1.07</v>
+        <v>1.65</v>
       </c>
       <c r="Q62" t="n">
         <v>2</v>
@@ -12445,7 +12445,7 @@
         <v>2</v>
       </c>
       <c r="V62" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="W62" t="n">
         <v>1.68</v>
@@ -12508,28 +12508,28 @@
         <v>2.16</v>
       </c>
       <c r="AQ62" t="n">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="AR62" t="n">
-        <v>17.5</v>
+        <v>2.36</v>
       </c>
       <c r="AS62" t="n">
         <v>2.5</v>
       </c>
       <c r="AT62" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AU62" t="n">
         <v>2.02</v>
       </c>
       <c r="AV62" t="n">
-        <v>11</v>
+        <v>2.26</v>
       </c>
       <c r="AW62" t="n">
         <v>2.42</v>
       </c>
       <c r="AX62" t="n">
-        <v>9.4</v>
+        <v>2.22</v>
       </c>
       <c r="AY62" t="n">
         <v>2.16</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -12788,7 +12788,7 @@
         <v>2.34</v>
       </c>
       <c r="G64" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="H64" t="n">
         <v>3.05</v>
@@ -12836,7 +12836,7 @@
         <v>1.4</v>
       </c>
       <c r="W64" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="X64" t="n">
         <v>1000</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -12988,7 +12988,7 @@
         <v>6.4</v>
       </c>
       <c r="I65" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J65" t="n">
         <v>4.2</v>
@@ -13027,7 +13027,7 @@
         <v>1.01</v>
       </c>
       <c r="V65" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W65" t="n">
         <v>2.58</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -13376,7 +13376,7 @@
         <v>3.35</v>
       </c>
       <c r="I67" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J67" t="n">
         <v>3</v>
@@ -13415,7 +13415,7 @@
         <v>1.01</v>
       </c>
       <c r="V67" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W67" t="n">
         <v>1.6</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -13561,7 +13561,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G68" t="n">
         <v>6.4</v>
@@ -13666,10 +13666,10 @@
         <v>1000</v>
       </c>
       <c r="AO68" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="AQ68" t="n">
         <v>6.8</v>
@@ -13678,10 +13678,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="AT68" t="n">
-        <v>1.03</v>
+        <v>2.36</v>
       </c>
       <c r="AU68" t="n">
         <v>6.6</v>
@@ -13690,41 +13690,41 @@
         <v>6.6</v>
       </c>
       <c r="AW68" t="n">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="AX68" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="AY68" t="n">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="AZ68" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BA68" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="BB68" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="BC68" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="BD68" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="BE68" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="BF68" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BG68" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -13779,10 +13779,10 @@
         <v>1.06</v>
       </c>
       <c r="N69" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O69" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P69" t="n">
         <v>1.98</v>
@@ -13791,16 +13791,16 @@
         <v>1.86</v>
       </c>
       <c r="R69" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S69" t="n">
         <v>3.15</v>
       </c>
       <c r="T69" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="U69" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="V69" t="n">
         <v>1.61</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -13997,10 +13997,10 @@
         <v>1.84</v>
       </c>
       <c r="V70" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W70" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X70" t="n">
         <v>1000</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -14173,7 +14173,7 @@
         <v>1.53</v>
       </c>
       <c r="P71" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q71" t="n">
         <v>2.62</v>
@@ -14293,7 +14293,7 @@
         <v>44</v>
       </c>
       <c r="BD71" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BE71" t="n">
         <v>46</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
         <v>1.78</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R72" t="n">
         <v>1.22</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -14564,7 +14564,7 @@
         <v>1.84</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R73" t="n">
         <v>1.26</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -14773,7 +14773,7 @@
         <v>1.01</v>
       </c>
       <c r="V74" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W74" t="n">
         <v>1.53</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -15525,7 +15525,7 @@
         <v>1.01</v>
       </c>
       <c r="N78" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O78" t="n">
         <v>1.35</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -15806,22 +15806,22 @@
         <v>2.16</v>
       </c>
       <c r="AQ79" t="n">
-        <v>2.16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR79" t="n">
-        <v>2.32</v>
+        <v>18</v>
       </c>
       <c r="AS79" t="n">
         <v>2.42</v>
       </c>
       <c r="AT79" t="n">
-        <v>2.08</v>
+        <v>7.4</v>
       </c>
       <c r="AU79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV79" t="n">
-        <v>2.22</v>
+        <v>12</v>
       </c>
       <c r="AW79" t="n">
         <v>2.4</v>
@@ -15830,7 +15830,7 @@
         <v>10</v>
       </c>
       <c r="AY79" t="n">
-        <v>2.18</v>
+        <v>9.6</v>
       </c>
       <c r="AZ79" t="n">
         <v>2.28</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -16277,16 +16277,16 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G82" t="n">
         <v>1.47</v>
       </c>
       <c r="H82" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I82" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J82" t="n">
         <v>5</v>
@@ -16322,13 +16322,13 @@
         <v>2</v>
       </c>
       <c r="U82" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V82" t="n">
         <v>1.13</v>
       </c>
       <c r="W82" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X82" t="n">
         <v>18.5</v>
@@ -16406,7 +16406,7 @@
         <v>27</v>
       </c>
       <c r="AW82" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AX82" t="n">
         <v>8.4</v>
@@ -16415,7 +16415,7 @@
         <v>10</v>
       </c>
       <c r="AZ82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA82" t="n">
         <v>85</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -16665,7 +16665,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G84" t="n">
         <v>2.08</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -17832,19 +17832,19 @@
         <v>2.48</v>
       </c>
       <c r="G90" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H90" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I90" t="n">
+        <v>970</v>
+      </c>
+      <c r="J90" t="n">
+        <v>2</v>
+      </c>
+      <c r="K90" t="n">
         <v>4.1</v>
-      </c>
-      <c r="J90" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="K90" t="n">
-        <v>3.95</v>
       </c>
       <c r="L90" t="n">
         <v>1.01</v>
@@ -17877,10 +17877,10 @@
         <v>1.01</v>
       </c>
       <c r="V90" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W90" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="X90" t="n">
         <v>1000</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
         <v>2.46</v>
       </c>
       <c r="I91" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J91" t="n">
         <v>3.15</v>
@@ -18050,7 +18050,7 @@
         <v>1.9</v>
       </c>
       <c r="O91" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P91" t="n">
         <v>1.9</v>
@@ -18059,70 +18059,70 @@
         <v>1.96</v>
       </c>
       <c r="R91" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="S91" t="n">
-        <v>1.96</v>
+        <v>2.92</v>
       </c>
       <c r="T91" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="U91" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V91" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W91" t="n">
         <v>1.39</v>
       </c>
       <c r="X91" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y91" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z91" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA91" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB91" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC91" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD91" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE91" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF91" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG91" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH91" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI91" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ91" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK91" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL91" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM91" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN91" t="n">
         <v>1000</v>
@@ -18131,62 +18131,62 @@
         <v>1000</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AT91" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AU91" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="AV91" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="AW91" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AX91" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY91" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ91" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BA91" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BB91" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BC91" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BD91" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BE91" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BF91" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BG91" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -18235,7 +18235,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M92" t="n">
         <v>1.01</v>
@@ -18253,7 +18253,7 @@
         <v>1.01</v>
       </c>
       <c r="R92" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S92" t="n">
         <v>1.01</v>
@@ -18325,52 +18325,52 @@
         <v>1000</v>
       </c>
       <c r="AP92" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ92" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR92" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AS92" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT92" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU92" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV92" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW92" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX92" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY92" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ92" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA92" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB92" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BC92" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD92" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BE92" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF92" t="n">
         <v>1.01</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH92"/>
+  <dimension ref="A1:BH93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="G3" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
         <v>1.88</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
         <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U3" t="n">
         <v>2.14</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="X3" t="n">
         <v>19</v>
@@ -1017,10 +1017,10 @@
         <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>21</v>
@@ -1029,7 +1029,7 @@
         <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG3" t="n">
         <v>13</v>
@@ -1041,13 +1041,13 @@
         <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AK3" t="n">
         <v>25</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM3" t="n">
         <v>120</v>
@@ -1056,7 +1056,7 @@
         <v>16</v>
       </c>
       <c r="AO3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP3" t="n">
         <v>13.5</v>
@@ -1065,22 +1065,22 @@
         <v>14</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
         <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX3" t="n">
         <v>11</v>
@@ -1092,29 +1092,29 @@
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC3" t="n">
         <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
         <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
         <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.04</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.02</v>
       </c>
       <c r="V4" t="n">
         <v>1.31</v>
@@ -1199,7 +1199,7 @@
         <v>1.87</v>
       </c>
       <c r="X4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y4" t="n">
         <v>14</v>
@@ -1208,16 +1208,16 @@
         <v>29</v>
       </c>
       <c r="AA4" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE4" t="n">
         <v>55</v>
@@ -1229,13 +1229,13 @@
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK4" t="n">
         <v>23</v>
@@ -1244,13 +1244,13 @@
         <v>40</v>
       </c>
       <c r="AM4" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
         <v>17</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP4" t="n">
         <v>11.5</v>
@@ -1265,7 +1265,7 @@
         <v>36</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU4" t="n">
         <v>7</v>
@@ -1286,13 +1286,13 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BB4" t="n">
         <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
         <v>34</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="G8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H8" t="n">
         <v>6.2</v>
@@ -1936,7 +1936,7 @@
         <v>4.7</v>
       </c>
       <c r="K8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.25</v>
@@ -1945,34 +1945,34 @@
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S8" t="n">
         <v>2.52</v>
       </c>
       <c r="T8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U8" t="n">
         <v>2.16</v>
       </c>
       <c r="V8" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X8" t="n">
         <v>26</v>
@@ -1993,7 +1993,7 @@
         <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE8" t="n">
         <v>85</v>
@@ -2023,25 +2023,25 @@
         <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AO8" t="n">
         <v>80</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU8" t="n">
         <v>10</v>
@@ -2050,7 +2050,7 @@
         <v>19</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX8" t="n">
         <v>9.4</v>
@@ -2062,29 +2062,29 @@
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB8" t="n">
         <v>12.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF8" t="n">
         <v>5.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H9" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J9" t="n">
         <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,34 +2139,34 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
         <v>3.45</v>
       </c>
       <c r="T9" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="U9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X9" t="n">
         <v>17.5</v>
@@ -2184,7 +2184,7 @@
         <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
         <v>20</v>
@@ -2226,37 +2226,37 @@
         <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU9" t="n">
         <v>7.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
         <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB9" t="n">
         <v>20</v>
@@ -2265,20 +2265,20 @@
         <v>18</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.27</v>
@@ -2333,34 +2333,34 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="R10" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S10" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="T10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X10" t="n">
         <v>26</v>
@@ -2378,7 +2378,7 @@
         <v>14</v>
       </c>
       <c r="AC10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD10" t="n">
         <v>16</v>
@@ -2390,10 +2390,10 @@
         <v>16.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI10" t="n">
         <v>46</v>
@@ -2429,31 +2429,31 @@
         <v>44</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AU10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV10" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC10" t="n">
         <v>17</v>
@@ -2462,17 +2462,17 @@
         <v>21</v>
       </c>
       <c r="BE10" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG10" t="n">
         <v>19.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
         <v>3.05</v>
       </c>
       <c r="I11" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="J11" t="n">
         <v>3.15</v>
@@ -2581,7 +2581,7 @@
         <v>44</v>
       </c>
       <c r="AF11" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AG11" t="n">
         <v>14</v>
@@ -2614,59 +2614,59 @@
         <v>12</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="AR11" t="n">
         <v>17</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.4</v>
+        <v>3.5</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX11" t="n">
         <v>11.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.4</v>
+        <v>3.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC11" t="n">
         <v>17.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF11" t="n">
         <v>12.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G12" t="n">
         <v>2.24</v>
@@ -2712,7 +2712,7 @@
         <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L12" t="n">
         <v>1.45</v>
@@ -2739,7 +2739,7 @@
         <v>4.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U12" t="n">
         <v>1.94</v>
@@ -2748,13 +2748,13 @@
         <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X12" t="n">
         <v>13.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
         <v>28</v>
@@ -2775,13 +2775,13 @@
         <v>60</v>
       </c>
       <c r="AF12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
         <v>75</v>
@@ -2814,7 +2814,7 @@
         <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT12" t="n">
         <v>7.4</v>
@@ -2826,7 +2826,7 @@
         <v>14.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
@@ -2838,29 +2838,29 @@
         <v>15.5</v>
       </c>
       <c r="BA12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB12" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB12" t="n">
-        <v>7</v>
-      </c>
       <c r="BC12" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF12" t="n">
         <v>17.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G13" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H13" t="n">
         <v>2.16</v>
       </c>
       <c r="I13" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J13" t="n">
         <v>3.55</v>
@@ -2939,10 +2939,10 @@
         <v>2.42</v>
       </c>
       <c r="V13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X13" t="n">
         <v>21</v>
@@ -2954,7 +2954,7 @@
         <v>16</v>
       </c>
       <c r="AA13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB13" t="n">
         <v>16.5</v>
@@ -2966,7 +2966,7 @@
         <v>12</v>
       </c>
       <c r="AE13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF13" t="n">
         <v>27</v>
@@ -2975,7 +2975,7 @@
         <v>15.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AI13" t="n">
         <v>34</v>
@@ -3020,7 +3020,7 @@
         <v>9.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX13" t="n">
         <v>19.5</v>
@@ -3032,10 +3032,10 @@
         <v>12.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BC13" t="n">
         <v>28</v>
@@ -3044,7 +3044,7 @@
         <v>32</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF13" t="n">
         <v>23</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -3094,13 +3094,13 @@
         <v>2.56</v>
       </c>
       <c r="I14" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J14" t="n">
         <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L14" t="n">
         <v>1.36</v>
@@ -3202,7 +3202,7 @@
         <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT14" t="n">
         <v>9.199999999999999</v>
@@ -3214,7 +3214,7 @@
         <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX14" t="n">
         <v>14.5</v>
@@ -3226,19 +3226,19 @@
         <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF14" t="n">
         <v>28</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -3288,10 +3288,10 @@
         <v>5.5</v>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K15" t="n">
         <v>4.6</v>
@@ -3303,10 +3303,10 @@
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P15" t="n">
         <v>2.06</v>
@@ -3321,16 +3321,16 @@
         <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V15" t="n">
         <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X15" t="n">
         <v>19</v>
@@ -3363,7 +3363,7 @@
         <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI15" t="n">
         <v>95</v>
@@ -3396,7 +3396,7 @@
         <v>6</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT15" t="n">
         <v>7.8</v>
@@ -3405,10 +3405,10 @@
         <v>8.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX15" t="n">
         <v>9.199999999999999</v>
@@ -3429,10 +3429,10 @@
         <v>13.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF15" t="n">
         <v>8.199999999999999</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>4.9</v>
       </c>
       <c r="G16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H16" t="n">
         <v>1.77</v>
@@ -3497,7 +3497,7 @@
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
         <v>1.33</v>
@@ -3527,7 +3527,7 @@
         <v>1.23</v>
       </c>
       <c r="X16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y16" t="n">
         <v>8.4</v>
@@ -3542,7 +3542,7 @@
         <v>17</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
         <v>9.800000000000001</v>
@@ -3599,7 +3599,7 @@
         <v>8.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW16" t="n">
         <v>17</v>
@@ -3611,32 +3611,32 @@
         <v>17.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC16" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BE16" t="n">
         <v>16</v>
       </c>
       <c r="BF16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BG16" t="n">
         <v>10.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
         <v>4.1</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3718,7 +3718,7 @@
         <v>1.18</v>
       </c>
       <c r="W17" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X17" t="n">
         <v>24</v>
@@ -3751,7 +3751,7 @@
         <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI17" t="n">
         <v>75</v>
@@ -3784,7 +3784,7 @@
         <v>6.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT17" t="n">
         <v>8.4</v>
@@ -3796,7 +3796,7 @@
         <v>19</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX17" t="n">
         <v>9.199999999999999</v>
@@ -3808,7 +3808,7 @@
         <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB17" t="n">
         <v>13.5</v>
@@ -3817,20 +3817,20 @@
         <v>13.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF17" t="n">
         <v>6.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
         <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -3990,31 +3990,31 @@
         <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AX18" t="n">
         <v>27</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AZ18" t="n">
         <v>15</v>
       </c>
       <c r="BA18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC18" t="n">
         <v>38</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF18" t="n">
         <v>36</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -4058,13 +4058,13 @@
         <v>2.7</v>
       </c>
       <c r="G19" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="H19" t="n">
         <v>2.5</v>
       </c>
       <c r="I19" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J19" t="n">
         <v>3.75</v>
@@ -4088,13 +4088,13 @@
         <v>2.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S19" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T19" t="n">
         <v>1.61</v>
@@ -4103,10 +4103,10 @@
         <v>2.46</v>
       </c>
       <c r="V19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X19" t="n">
         <v>24</v>
@@ -4139,7 +4139,7 @@
         <v>13.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AI19" t="n">
         <v>34</v>
@@ -4196,19 +4196,19 @@
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB19" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BC19" t="n">
         <v>7</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>6.4</v>
       </c>
       <c r="BD19" t="n">
         <v>6.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BF19" t="n">
         <v>16.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -4333,7 +4333,7 @@
         <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI20" t="n">
         <v>44</v>
@@ -4363,7 +4363,7 @@
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS20" t="n">
         <v>40</v>
@@ -4390,19 +4390,19 @@
         <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BC20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BF20" t="n">
         <v>12.5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
         <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
@@ -4551,62 +4551,62 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AZ21" t="n">
         <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>1.6</v>
       </c>
       <c r="G22" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H22" t="n">
         <v>5.1</v>
@@ -4670,13 +4670,13 @@
         <v>2.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="R22" t="n">
         <v>1.53</v>
       </c>
       <c r="S22" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -4688,7 +4688,7 @@
         <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
         <v>3.75</v>
       </c>
       <c r="J23" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K23" t="n">
         <v>3.9</v>
@@ -4861,13 +4861,13 @@
         <v>1.27</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
         <v>1.76</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -4897,7 +4897,7 @@
         <v>70</v>
       </c>
       <c r="AB23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC23" t="n">
         <v>8.6</v>
@@ -4906,7 +4906,7 @@
         <v>15</v>
       </c>
       <c r="AE23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF23" t="n">
         <v>14.5</v>
@@ -4924,16 +4924,16 @@
         <v>27</v>
       </c>
       <c r="AK23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM23" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO23" t="n">
         <v>44</v>
@@ -4948,7 +4948,7 @@
         <v>23</v>
       </c>
       <c r="AS23" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT23" t="n">
         <v>9.800000000000001</v>
@@ -4966,13 +4966,13 @@
         <v>13</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ23" t="n">
         <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB23" t="n">
         <v>24</v>
@@ -4981,20 +4981,20 @@
         <v>19</v>
       </c>
       <c r="BD23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BF23" t="n">
         <v>12.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G25" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H25" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="J25" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L25" t="n">
         <v>1.3</v>
@@ -5243,7 +5243,7 @@
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
         <v>1.24</v>
@@ -5255,10 +5255,10 @@
         <v>1.71</v>
       </c>
       <c r="R25" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
         <v>1.64</v>
@@ -5270,7 +5270,7 @@
         <v>1.35</v>
       </c>
       <c r="W25" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X25" t="n">
         <v>22</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G27" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H27" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I27" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="J27" t="n">
         <v>3.95</v>
@@ -5631,13 +5631,13 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O27" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P27" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q27" t="n">
         <v>1.5</v>
@@ -5658,7 +5658,7 @@
         <v>1.52</v>
       </c>
       <c r="W27" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
         <v>3.15</v>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
         <v>3.5</v>
@@ -5834,13 +5834,13 @@
         <v>2.56</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R28" t="n">
         <v>1.63</v>
       </c>
       <c r="S28" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="T28" t="n">
         <v>1.44</v>
@@ -5852,7 +5852,7 @@
         <v>1.33</v>
       </c>
       <c r="W28" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X28" t="n">
         <v>32</v>
@@ -5867,7 +5867,7 @@
         <v>65</v>
       </c>
       <c r="AB28" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC28" t="n">
         <v>12.5</v>
@@ -5909,7 +5909,7 @@
         <v>25</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ28" t="n">
         <v>14</v>
@@ -5945,7 +5945,7 @@
         <v>1.03</v>
       </c>
       <c r="BB28" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC28" t="n">
         <v>14.5</v>
@@ -5960,11 +5960,11 @@
         <v>7.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
         <v>1.12</v>
       </c>
       <c r="P29" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q29" t="n">
         <v>1.45</v>
@@ -6034,7 +6034,7 @@
         <v>1.64</v>
       </c>
       <c r="S29" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -6043,10 +6043,10 @@
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W29" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X29" t="n">
         <v>40</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>1.45</v>
       </c>
       <c r="G30" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="H30" t="n">
         <v>5.1</v>
@@ -6201,7 +6201,7 @@
         <v>7.6</v>
       </c>
       <c r="J30" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="K30" t="n">
         <v>6.2</v>
@@ -6213,7 +6213,7 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O30" t="n">
         <v>1.13</v>
@@ -6225,10 +6225,10 @@
         <v>1.38</v>
       </c>
       <c r="R30" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="S30" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="T30" t="n">
         <v>1.55</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -6386,16 +6386,16 @@
         <v>1.47</v>
       </c>
       <c r="G31" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="H31" t="n">
         <v>7.6</v>
       </c>
       <c r="I31" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J31" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="K31" t="n">
         <v>4.7</v>
@@ -6407,7 +6407,7 @@
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O31" t="n">
         <v>1.39</v>
@@ -6416,25 +6416,25 @@
         <v>1.71</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="R31" t="n">
         <v>1.26</v>
       </c>
       <c r="S31" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="U31" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="V31" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W31" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="X31" t="n">
         <v>970</v>
@@ -6485,13 +6485,13 @@
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AQ31" t="n">
         <v>3.85</v>
@@ -6500,25 +6500,25 @@
         <v>4.3</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT31" t="n">
         <v>4.8</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="AV31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW31" t="n">
         <v>4.4</v>
       </c>
       <c r="AX31" t="n">
-        <v>5.9</v>
+        <v>3.05</v>
       </c>
       <c r="AY31" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="AZ31" t="n">
         <v>4</v>
@@ -6530,23 +6530,23 @@
         <v>10</v>
       </c>
       <c r="BC31" t="n">
-        <v>14</v>
+        <v>3.8</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF31" t="n">
         <v>8</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
         <v>2.54</v>
       </c>
       <c r="G32" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H32" t="n">
         <v>3</v>
@@ -6589,10 +6589,10 @@
         <v>3.45</v>
       </c>
       <c r="J32" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="K32" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -6610,7 +6610,7 @@
         <v>1.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R32" t="n">
         <v>1.26</v>
@@ -6625,10 +6625,10 @@
         <v>1.81</v>
       </c>
       <c r="V32" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W32" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X32" t="n">
         <v>13.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>1.62</v>
       </c>
       <c r="G33" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="H33" t="n">
         <v>4.6</v>
@@ -6786,13 +6786,13 @@
         <v>4.5</v>
       </c>
       <c r="K33" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N33" t="n">
         <v>6.2</v>
@@ -6807,10 +6807,10 @@
         <v>1.53</v>
       </c>
       <c r="R33" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S33" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T33" t="n">
         <v>1.56</v>
@@ -6819,10 +6819,10 @@
         <v>2.46</v>
       </c>
       <c r="V33" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W33" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="X33" t="n">
         <v>40</v>
@@ -6843,7 +6843,7 @@
         <v>14.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE33" t="n">
         <v>65</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -6965,16 +6965,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G34" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H34" t="n">
         <v>5</v>
       </c>
       <c r="I34" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J34" t="n">
         <v>3.85</v>
@@ -6995,34 +6995,34 @@
         <v>1.3</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R34" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
         <v>3.2</v>
       </c>
       <c r="T34" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U34" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V34" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W34" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X34" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Y34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="n">
         <v>42</v>
@@ -7043,7 +7043,7 @@
         <v>70</v>
       </c>
       <c r="AF34" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG34" t="n">
         <v>10</v>
@@ -7055,7 +7055,7 @@
         <v>70</v>
       </c>
       <c r="AJ34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK34" t="n">
         <v>970</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G35" t="n">
         <v>1.82</v>
@@ -7171,10 +7171,10 @@
         <v>6.6</v>
       </c>
       <c r="J35" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K35" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7183,7 +7183,7 @@
         <v>1.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O35" t="n">
         <v>1.44</v>
@@ -7213,7 +7213,7 @@
         <v>2.2</v>
       </c>
       <c r="X35" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y35" t="n">
         <v>19.5</v>
@@ -7276,7 +7276,7 @@
         <v>4</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT35" t="n">
         <v>5.8</v>
@@ -7309,20 +7309,20 @@
         <v>19.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF35" t="n">
         <v>12</v>
       </c>
       <c r="BG35" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G36" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H36" t="n">
         <v>4.2</v>
@@ -7368,7 +7368,7 @@
         <v>3.4</v>
       </c>
       <c r="K36" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -7383,7 +7383,7 @@
         <v>1.33</v>
       </c>
       <c r="P36" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q36" t="n">
         <v>1.87</v>
@@ -7404,7 +7404,7 @@
         <v>1.24</v>
       </c>
       <c r="W36" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -7753,10 +7753,10 @@
         <v>3.2</v>
       </c>
       <c r="J38" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K38" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -7813,7 +7813,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD38" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE38" t="n">
         <v>40</v>
@@ -7846,10 +7846,10 @@
         <v>25</v>
       </c>
       <c r="AO38" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AP38" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AQ38" t="n">
         <v>10</v>
@@ -7858,10 +7858,10 @@
         <v>16</v>
       </c>
       <c r="AS38" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AU38" t="n">
         <v>6.6</v>
@@ -7870,7 +7870,7 @@
         <v>10.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX38" t="n">
         <v>13.5</v>
@@ -7879,32 +7879,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ38" t="n">
-        <v>12</v>
+        <v>4.1</v>
       </c>
       <c r="BA38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC38" t="n">
         <v>4.6</v>
       </c>
-      <c r="BB38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD38" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF38" t="n">
         <v>16.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
         <v>2.38</v>
       </c>
       <c r="G42" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H42" t="n">
         <v>2.98</v>
@@ -8565,10 +8565,10 @@
         <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W42" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -8938,13 +8938,13 @@
         <v>2.34</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="R44" t="n">
         <v>1.25</v>
       </c>
       <c r="S44" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -9905,7 +9905,7 @@
         <v>1.17</v>
       </c>
       <c r="P49" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q49" t="n">
         <v>1.58</v>
@@ -9971,7 +9971,7 @@
         <v>46</v>
       </c>
       <c r="AL49" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM49" t="n">
         <v>60</v>
@@ -10031,14 +10031,14 @@
         <v>6.2</v>
       </c>
       <c r="BF49" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG49" t="n">
         <v>6.2</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -10505,7 +10505,7 @@
         <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W52" t="n">
         <v>1.54</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -11039,13 +11039,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G55" t="n">
         <v>2.86</v>
       </c>
       <c r="H55" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="I55" t="n">
         <v>3.15</v>
@@ -11063,22 +11063,22 @@
         <v>1.06</v>
       </c>
       <c r="N55" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="O55" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P55" t="n">
         <v>2.02</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="R55" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S55" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="T55" t="n">
         <v>1.46</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -11260,7 +11260,7 @@
         <v>1.33</v>
       </c>
       <c r="O56" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P56" t="n">
         <v>1.33</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -12517,7 +12517,7 @@
         <v>2.5</v>
       </c>
       <c r="AT62" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AU62" t="n">
         <v>2.02</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -12809,7 +12809,7 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="O64" t="n">
         <v>1.29</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -13370,13 +13370,13 @@
         <v>2.2</v>
       </c>
       <c r="G67" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="H67" t="n">
         <v>3.35</v>
       </c>
       <c r="I67" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J67" t="n">
         <v>3</v>
@@ -13415,10 +13415,10 @@
         <v>1.01</v>
       </c>
       <c r="V67" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W67" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="X67" t="n">
         <v>1000</v>
@@ -13530,14 +13530,14 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Scottish Premiership</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -13552,186 +13552,186 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>St Johnstone</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F68" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I68" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J68" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K68" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N68" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O68" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X68" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF68" t="n">
         <v>4.5</v>
       </c>
-      <c r="G68" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H68" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="I68" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="J68" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K68" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L68" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M68" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N68" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O68" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P68" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R68" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S68" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T68" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="U68" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V68" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X68" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO68" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP68" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AQ68" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS68" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AT68" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AU68" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV68" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW68" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AX68" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AY68" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AZ68" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BA68" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BB68" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BC68" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BD68" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BE68" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BF68" t="n">
-        <v>2.58</v>
-      </c>
       <c r="BG68" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Scottish Premiership</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -13746,179 +13746,179 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="G69" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I69" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K69" t="n">
         <v>3.2</v>
       </c>
-      <c r="H69" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I69" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J69" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K69" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L69" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M69" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="N69" t="n">
-        <v>3.9</v>
+        <v>2.82</v>
       </c>
       <c r="O69" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="P69" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.86</v>
+        <v>2.62</v>
       </c>
       <c r="R69" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="S69" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="T69" t="n">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="U69" t="n">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="V69" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W69" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="X69" t="n">
-        <v>17.5</v>
+        <v>8.6</v>
       </c>
       <c r="Y69" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="Z69" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF69" t="n">
         <v>20</v>
       </c>
-      <c r="AA69" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB69" t="n">
+      <c r="AG69" t="n">
         <v>15</v>
       </c>
-      <c r="AC69" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD69" t="n">
+      <c r="AH69" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR69" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE69" t="n">
+      <c r="AS69" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW69" t="n">
         <v>32</v>
       </c>
-      <c r="AF69" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG69" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH69" t="n">
+      <c r="AX69" t="n">
         <v>19</v>
       </c>
-      <c r="AI69" t="n">
+      <c r="AY69" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC69" t="n">
         <v>44</v>
       </c>
-      <c r="AJ69" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK69" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL69" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM69" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN69" t="n">
+      <c r="BD69" t="n">
         <v>34</v>
       </c>
-      <c r="AO69" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP69" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ69" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR69" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS69" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT69" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU69" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV69" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW69" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX69" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY69" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ69" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA69" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB69" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC69" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD69" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BE69" t="n">
-        <v>4.9</v>
+        <v>46</v>
       </c>
       <c r="BF69" t="n">
-        <v>4.5</v>
+        <v>55</v>
       </c>
       <c r="BG69" t="n">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -14112,14 +14112,14 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -14134,179 +14134,179 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>St Johnstone</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="G71" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="H71" t="n">
-        <v>2.56</v>
+        <v>1.77</v>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="J71" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="K71" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="L71" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="M71" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N71" t="n">
-        <v>2.82</v>
+        <v>3.75</v>
       </c>
       <c r="O71" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="P71" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="R71" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="S71" t="n">
-        <v>5.4</v>
+        <v>2.66</v>
       </c>
       <c r="T71" t="n">
-        <v>2.14</v>
+        <v>1.52</v>
       </c>
       <c r="U71" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="V71" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="W71" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="X71" t="n">
-        <v>8.6</v>
+        <v>24</v>
       </c>
       <c r="Y71" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="Z71" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AA71" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AB71" t="n">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="AC71" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BG71" t="n">
         <v>7.2</v>
       </c>
-      <c r="AD71" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE71" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF71" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG71" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ71" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK71" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL71" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM71" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN71" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO71" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP71" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ71" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR71" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS71" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT71" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU71" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV71" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW71" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX71" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY71" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ71" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA71" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB71" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC71" t="n">
-        <v>44</v>
-      </c>
-      <c r="BD71" t="n">
-        <v>60</v>
-      </c>
-      <c r="BE71" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF71" t="n">
-        <v>55</v>
-      </c>
-      <c r="BG71" t="n">
-        <v>32</v>
-      </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -14343,7 +14343,7 @@
         <v>5.4</v>
       </c>
       <c r="H72" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="I72" t="n">
         <v>2.12</v>
@@ -14352,7 +14352,7 @@
         <v>3.4</v>
       </c>
       <c r="K72" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L72" t="n">
         <v>1.35</v>
@@ -14379,10 +14379,10 @@
         <v>3.4</v>
       </c>
       <c r="T72" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U72" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="V72" t="n">
         <v>1.89</v>
@@ -14391,13 +14391,13 @@
         <v>1.23</v>
       </c>
       <c r="X72" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y72" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z72" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA72" t="n">
         <v>30</v>
@@ -14412,16 +14412,16 @@
         <v>13.5</v>
       </c>
       <c r="AE72" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF72" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG72" t="n">
         <v>24</v>
       </c>
       <c r="AH72" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI72" t="n">
         <v>55</v>
@@ -14445,28 +14445,28 @@
         <v>1000</v>
       </c>
       <c r="AP72" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AQ72" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="AR72" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS72" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="AT72" t="n">
         <v>10.5</v>
       </c>
       <c r="AU72" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AV72" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="AW72" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="AX72" t="n">
         <v>23</v>
@@ -14475,32 +14475,32 @@
         <v>13.5</v>
       </c>
       <c r="AZ72" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="BA72" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="BB72" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BC72" t="n">
         <v>2.84</v>
       </c>
-      <c r="BC72" t="n">
-        <v>2.74</v>
-      </c>
       <c r="BD72" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="BE72" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="BF72" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="BG72" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -14558,7 +14558,7 @@
         <v>1.84</v>
       </c>
       <c r="O73" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P73" t="n">
         <v>1.84</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
         <v>2.9</v>
       </c>
       <c r="I74" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="J74" t="n">
         <v>3.1</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -14922,7 +14922,7 @@
         <v>1.39</v>
       </c>
       <c r="G75" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H75" t="n">
         <v>5.7</v>
@@ -14943,13 +14943,13 @@
         <v>1.01</v>
       </c>
       <c r="N75" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="O75" t="n">
         <v>1.26</v>
       </c>
       <c r="P75" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q75" t="n">
         <v>1.8</v>
@@ -14970,7 +14970,7 @@
         <v>1.09</v>
       </c>
       <c r="W75" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="X75" t="n">
         <v>1000</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -16206,7 +16206,7 @@
         <v>2.28</v>
       </c>
       <c r="AU81" t="n">
-        <v>10</v>
+        <v>2.4</v>
       </c>
       <c r="AV81" t="n">
         <v>2.6</v>
@@ -16230,7 +16230,7 @@
         <v>2.28</v>
       </c>
       <c r="BC81" t="n">
-        <v>2.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD81" t="n">
         <v>2.58</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -16385,13 +16385,13 @@
         <v>140</v>
       </c>
       <c r="AP82" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ82" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR82" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AS82" t="n">
         <v>75</v>
@@ -16406,7 +16406,7 @@
         <v>27</v>
       </c>
       <c r="AW82" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AX82" t="n">
         <v>8.4</v>
@@ -16418,7 +16418,7 @@
         <v>23</v>
       </c>
       <c r="BA82" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="BB82" t="n">
         <v>11.5</v>
@@ -16427,7 +16427,7 @@
         <v>13.5</v>
       </c>
       <c r="BD82" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE82" t="n">
         <v>60</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -16698,10 +16698,10 @@
         <v>1.7</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="R84" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S84" t="n">
         <v>3.75</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -17992,14 +17992,14 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -18014,31 +18014,31 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medellin</t>
+          <t>Sportivo San Lorenzo</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
         <v>1.01</v>
@@ -18047,82 +18047,82 @@
         <v>1.01</v>
       </c>
       <c r="N91" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="O91" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="P91" t="n">
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="R91" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S91" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="T91" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="U91" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V91" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="W91" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="X91" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y91" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z91" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA91" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB91" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC91" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD91" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE91" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF91" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG91" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AH91" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI91" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ91" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK91" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL91" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM91" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN91" t="n">
         <v>1000</v>
@@ -18131,69 +18131,69 @@
         <v>1000</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="AQ91" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AR91" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS91" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT91" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU91" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="AV91" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="AW91" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX91" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY91" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ91" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BA91" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB91" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BC91" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD91" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BE91" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BF91" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="BG91" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -18208,31 +18208,31 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo</t>
+          <t>Atletico Nacional Medellin</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L92" t="n">
         <v>1.01</v>
@@ -18241,82 +18241,82 @@
         <v>1.01</v>
       </c>
       <c r="N92" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="O92" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="P92" t="n">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R92" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S92" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="T92" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="U92" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V92" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="W92" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="X92" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y92" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z92" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA92" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB92" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC92" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD92" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE92" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF92" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG92" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH92" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI92" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ92" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK92" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL92" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM92" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN92" t="n">
         <v>1000</v>
@@ -18325,62 +18325,256 @@
         <v>1000</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="AR92" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS92" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AT92" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AU92" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="AV92" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="AW92" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AX92" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY92" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ92" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BA92" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BB92" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BC92" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BD92" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BE92" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BF92" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BG92" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aucas</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G93" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I93" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J93" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K93" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P93" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S93" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V93" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W93" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH93" t="inlineStr">
+        <is>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="G2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I2" t="n">
         <v>2.24</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
         <v>4.4</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H3" t="n">
         <v>4.2</v>
@@ -969,19 +969,19 @@
         <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>1.88</v>
@@ -1002,7 +1002,7 @@
         <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X3" t="n">
         <v>19</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G4" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
         <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
         <v>1.36</v>
@@ -1184,7 +1184,7 @@
         <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T4" t="n">
         <v>1.87</v>
@@ -1193,43 +1193,43 @@
         <v>2.04</v>
       </c>
       <c r="V4" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="X4" t="n">
         <v>12.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA4" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
         <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI4" t="n">
         <v>65</v>
@@ -1238,16 +1238,16 @@
         <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM4" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN4" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AO4" t="n">
         <v>60</v>
@@ -1256,40 +1256,40 @@
         <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU4" t="n">
         <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
         <v>27</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
         <v>20</v>
@@ -1301,14 +1301,14 @@
         <v>40</v>
       </c>
       <c r="BF4" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BG4" t="n">
         <v>30</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>3.35</v>
       </c>
       <c r="I6" t="n">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="J6" t="n">
         <v>1.03</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
         <v>2.08</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -1921,67 +1921,67 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G8" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="H8" t="n">
         <v>6.2</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J8" t="n">
         <v>4.7</v>
       </c>
       <c r="K8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
         <v>2.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U8" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
         <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="X8" t="n">
         <v>26</v>
       </c>
       <c r="Y8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="AA8" t="n">
         <v>190</v>
@@ -1990,28 +1990,28 @@
         <v>12.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AE8" t="n">
         <v>85</v>
       </c>
       <c r="AF8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
         <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AK8" t="n">
         <v>18</v>
@@ -2023,37 +2023,37 @@
         <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO8" t="n">
         <v>80</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.7</v>
+        <v>17.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.9</v>
+        <v>28</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.7</v>
+        <v>44</v>
       </c>
       <c r="AT8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV8" t="n">
         <v>19</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY8" t="n">
         <v>9.199999999999999</v>
@@ -2062,7 +2062,7 @@
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="BB8" t="n">
         <v>12.5</v>
@@ -2071,20 +2071,20 @@
         <v>13.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.7</v>
+        <v>22</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.6</v>
+        <v>36</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="H9" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,85 +2139,85 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T9" t="n">
         <v>1.82</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="X9" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA9" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB9" t="n">
         <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF9" t="n">
         <v>13.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK9" t="n">
         <v>26</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>27</v>
       </c>
       <c r="AL9" t="n">
         <v>40</v>
       </c>
       <c r="AM9" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AO9" t="n">
         <v>60</v>
@@ -2226,13 +2226,13 @@
         <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AT9" t="n">
         <v>8.199999999999999</v>
@@ -2244,19 +2244,19 @@
         <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AX9" t="n">
         <v>11</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
         <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BB9" t="n">
         <v>20</v>
@@ -2265,20 +2265,20 @@
         <v>18</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G10" t="n">
         <v>2.18</v>
@@ -2318,7 +2318,7 @@
         <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J10" t="n">
         <v>3.85</v>
@@ -2333,13 +2333,13 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q10" t="n">
         <v>1.63</v>
@@ -2357,10 +2357,10 @@
         <v>2.46</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X10" t="n">
         <v>26</v>
@@ -2396,13 +2396,13 @@
         <v>16.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ10" t="n">
         <v>28</v>
       </c>
       <c r="AK10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL10" t="n">
         <v>30</v>
@@ -2411,7 +2411,7 @@
         <v>75</v>
       </c>
       <c r="AN10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO10" t="n">
         <v>27</v>
@@ -2438,7 +2438,7 @@
         <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX10" t="n">
         <v>13.5</v>
@@ -2450,10 +2450,10 @@
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB10" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7</v>
       </c>
       <c r="BC10" t="n">
         <v>17</v>
@@ -2462,7 +2462,7 @@
         <v>21</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF10" t="n">
         <v>9.6</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
         <v>3.05</v>
       </c>
       <c r="I11" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="J11" t="n">
         <v>3.15</v>
@@ -2542,10 +2542,10 @@
         <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="T11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U11" t="n">
         <v>2.2</v>
@@ -2554,7 +2554,7 @@
         <v>1.39</v>
       </c>
       <c r="W11" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
         <v>20</v>
@@ -2611,22 +2611,22 @@
         <v>38</v>
       </c>
       <c r="AP11" t="n">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="AQ11" t="n">
         <v>3.7</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>3.75</v>
       </c>
       <c r="AS11" t="n">
         <v>4.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.5</v>
+        <v>9.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV11" t="n">
         <v>3.7</v>
@@ -2635,13 +2635,13 @@
         <v>4.3</v>
       </c>
       <c r="AX11" t="n">
-        <v>11.5</v>
+        <v>3.8</v>
       </c>
       <c r="AY11" t="n">
         <v>3.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="BA11" t="n">
         <v>4</v>
@@ -2650,7 +2650,7 @@
         <v>4.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>17.5</v>
+        <v>3.95</v>
       </c>
       <c r="BD11" t="n">
         <v>4.2</v>
@@ -2659,14 +2659,14 @@
         <v>4.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>12.5</v>
+        <v>3.65</v>
       </c>
       <c r="BG11" t="n">
         <v>4.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G12" t="n">
         <v>2.24</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
         <v>3.2</v>
@@ -2730,7 +2730,7 @@
         <v>1.74</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="R12" t="n">
         <v>1.28</v>
@@ -2739,13 +2739,13 @@
         <v>4.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
         <v>1.81</v>
@@ -2769,7 +2769,7 @@
         <v>7.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE12" t="n">
         <v>60</v>
@@ -2784,7 +2784,7 @@
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ12" t="n">
         <v>29</v>
@@ -2802,7 +2802,7 @@
         <v>22</v>
       </c>
       <c r="AO12" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AP12" t="n">
         <v>10</v>
@@ -2826,7 +2826,7 @@
         <v>14.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
@@ -2838,19 +2838,19 @@
         <v>15.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BD12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF12" t="n">
         <v>17.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G13" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="H13" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="I13" t="n">
         <v>2.32</v>
@@ -2906,7 +2906,7 @@
         <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
         <v>1.34</v>
@@ -2915,7 +2915,7 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
         <v>1.26</v>
@@ -2924,28 +2924,28 @@
         <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
         <v>2.94</v>
       </c>
       <c r="T13" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U13" t="n">
         <v>2.42</v>
       </c>
       <c r="V13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W13" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y13" t="n">
         <v>12.5</v>
@@ -2960,13 +2960,13 @@
         <v>16.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13" t="n">
         <v>12</v>
       </c>
       <c r="AE13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF13" t="n">
         <v>27</v>
@@ -2993,13 +2993,13 @@
         <v>75</v>
       </c>
       <c r="AN13" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO13" t="n">
         <v>15</v>
       </c>
       <c r="AP13" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
         <v>9.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX13" t="n">
         <v>19.5</v>
@@ -3032,7 +3032,7 @@
         <v>12.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB13" t="n">
         <v>9</v>
@@ -3044,7 +3044,7 @@
         <v>32</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF13" t="n">
         <v>23</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
         <v>3.15</v>
@@ -3094,7 +3094,7 @@
         <v>2.56</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J14" t="n">
         <v>3.15</v>
@@ -3109,22 +3109,22 @@
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R14" t="n">
         <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
         <v>1.84</v>
@@ -3133,7 +3133,7 @@
         <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W14" t="n">
         <v>1.46</v>
@@ -3142,10 +3142,10 @@
         <v>14</v>
       </c>
       <c r="Y14" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA14" t="n">
         <v>42</v>
@@ -3154,7 +3154,7 @@
         <v>11.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AD14" t="n">
         <v>15</v>
@@ -3175,10 +3175,10 @@
         <v>50</v>
       </c>
       <c r="AJ14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK14" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AL14" t="n">
         <v>55</v>
@@ -3187,7 +3187,7 @@
         <v>140</v>
       </c>
       <c r="AN14" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AO14" t="n">
         <v>32</v>
@@ -3202,7 +3202,7 @@
         <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT14" t="n">
         <v>9.199999999999999</v>
@@ -3214,7 +3214,7 @@
         <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX14" t="n">
         <v>14.5</v>
@@ -3226,19 +3226,19 @@
         <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.7</v>
+        <v>38</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.6</v>
+        <v>28</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF14" t="n">
         <v>28</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -3279,25 +3279,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="H15" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
@@ -3315,7 +3315,7 @@
         <v>1.81</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
         <v>3.1</v>
@@ -3324,13 +3324,13 @@
         <v>1.93</v>
       </c>
       <c r="U15" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="X15" t="n">
         <v>19</v>
@@ -3339,7 +3339,7 @@
         <v>23</v>
       </c>
       <c r="Z15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AA15" t="n">
         <v>180</v>
@@ -3348,7 +3348,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
         <v>27</v>
@@ -3366,7 +3366,7 @@
         <v>25</v>
       </c>
       <c r="AI15" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ15" t="n">
         <v>19.5</v>
@@ -3393,10 +3393,10 @@
         <v>18</v>
       </c>
       <c r="AR15" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT15" t="n">
         <v>7.8</v>
@@ -3405,13 +3405,13 @@
         <v>8.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY15" t="n">
         <v>8.4</v>
@@ -3420,29 +3420,29 @@
         <v>18</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BB15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC15" t="n">
         <v>13.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="H16" t="n">
         <v>1.77</v>
@@ -3497,40 +3497,40 @@
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V16" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W16" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z16" t="n">
         <v>11</v>
@@ -3542,7 +3542,7 @@
         <v>17</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
         <v>9.800000000000001</v>
@@ -3557,28 +3557,28 @@
         <v>20</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI16" t="n">
         <v>40</v>
       </c>
       <c r="AJ16" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AL16" t="n">
         <v>85</v>
       </c>
       <c r="AM16" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN16" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AO16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AP16" t="n">
         <v>12.5</v>
@@ -3596,7 +3596,7 @@
         <v>16</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16" t="n">
         <v>9.199999999999999</v>
@@ -3608,35 +3608,35 @@
         <v>34</v>
       </c>
       <c r="AY16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ16" t="n">
         <v>19</v>
       </c>
       <c r="BA16" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="BB16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BE16" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG16" t="n">
         <v>10.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G17" t="n">
         <v>1.69</v>
       </c>
       <c r="H17" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I17" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
         <v>4.1</v>
       </c>
       <c r="K17" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3697,13 +3697,13 @@
         <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R17" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
         <v>2.78</v>
@@ -3715,13 +3715,13 @@
         <v>2.12</v>
       </c>
       <c r="V17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y17" t="n">
         <v>25</v>
@@ -3757,10 +3757,10 @@
         <v>75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL17" t="n">
         <v>32</v>
@@ -3781,10 +3781,10 @@
         <v>19.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT17" t="n">
         <v>8.4</v>
@@ -3796,7 +3796,7 @@
         <v>19</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX17" t="n">
         <v>9.199999999999999</v>
@@ -3808,7 +3808,7 @@
         <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB17" t="n">
         <v>13.5</v>
@@ -3820,17 +3820,17 @@
         <v>6</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF17" t="n">
         <v>6.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
         <v>4.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
         <v>2.22</v>
@@ -3900,25 +3900,25 @@
         <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T18" t="n">
         <v>1.69</v>
       </c>
       <c r="U18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V18" t="n">
         <v>2.12</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X18" t="n">
         <v>23</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z18" t="n">
         <v>15</v>
@@ -3930,10 +3930,10 @@
         <v>24</v>
       </c>
       <c r="AC18" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>22</v>
@@ -3945,7 +3945,7 @@
         <v>23</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI18" t="n">
         <v>38</v>
@@ -3990,31 +3990,31 @@
         <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AX18" t="n">
         <v>27</v>
       </c>
       <c r="AY18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AZ18" t="n">
         <v>15</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BC18" t="n">
         <v>38</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF18" t="n">
         <v>36</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -4058,16 +4058,16 @@
         <v>2.7</v>
       </c>
       <c r="G19" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H19" t="n">
         <v>2.5</v>
       </c>
       <c r="I19" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K19" t="n">
         <v>4.1</v>
@@ -4085,7 +4085,7 @@
         <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q19" t="n">
         <v>1.69</v>
@@ -4100,7 +4100,7 @@
         <v>1.61</v>
       </c>
       <c r="U19" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V19" t="n">
         <v>1.6</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G20" t="n">
         <v>2.42</v>
@@ -4267,7 +4267,7 @@
         <v>3.85</v>
       </c>
       <c r="L20" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
@@ -4288,7 +4288,7 @@
         <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
         <v>1.66</v>
@@ -4321,7 +4321,7 @@
         <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
         <v>42</v>
@@ -4333,7 +4333,7 @@
         <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI20" t="n">
         <v>44</v>
@@ -4354,7 +4354,7 @@
         <v>16.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP20" t="n">
         <v>14.5</v>
@@ -4363,7 +4363,7 @@
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS20" t="n">
         <v>40</v>
@@ -4390,19 +4390,19 @@
         <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF20" t="n">
         <v>12.5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
         <v>5.1</v>
       </c>
       <c r="I22" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J22" t="n">
         <v>4.4</v>
@@ -4658,97 +4658,97 @@
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>2.56</v>
+        <v>5.6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P22" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R22" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="S22" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V22" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W22" t="n">
         <v>2.44</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AR22" t="n">
         <v>1.03</v>
@@ -4757,50 +4757,50 @@
         <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AW22" t="n">
         <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA22" t="n">
         <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BE22" t="n">
         <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
         <v>3.75</v>
       </c>
       <c r="J23" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K23" t="n">
         <v>3.9</v>
@@ -4867,7 +4867,7 @@
         <v>1.76</v>
       </c>
       <c r="R23" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -4885,7 +4885,7 @@
         <v>1.86</v>
       </c>
       <c r="X23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y23" t="n">
         <v>15.5</v>
@@ -4915,7 +4915,7 @@
         <v>10.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI23" t="n">
         <v>48</v>
@@ -4933,7 +4933,7 @@
         <v>80</v>
       </c>
       <c r="AN23" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AO23" t="n">
         <v>44</v>
@@ -4942,22 +4942,22 @@
         <v>15</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR23" t="n">
         <v>23</v>
       </c>
       <c r="AS23" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AT23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU23" t="n">
         <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
         <v>34</v>
@@ -4969,7 +4969,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA23" t="n">
         <v>32</v>
@@ -4984,17 +4984,17 @@
         <v>28</v>
       </c>
       <c r="BE23" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BF23" t="n">
         <v>12.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G25" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H25" t="n">
         <v>3.4</v>
       </c>
       <c r="I25" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J25" t="n">
         <v>3.7</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L25" t="n">
         <v>1.3</v>
@@ -5243,7 +5243,7 @@
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
         <v>1.24</v>
@@ -5267,10 +5267,10 @@
         <v>2.32</v>
       </c>
       <c r="V25" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W25" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X25" t="n">
         <v>22</v>
@@ -5294,7 +5294,7 @@
         <v>17.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF25" t="n">
         <v>17.5</v>
@@ -5309,7 +5309,7 @@
         <v>50</v>
       </c>
       <c r="AJ25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK25" t="n">
         <v>25</v>
@@ -5324,65 +5324,65 @@
         <v>15</v>
       </c>
       <c r="AO25" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP25" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT25" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU25" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV25" t="n">
         <v>11.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY25" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB25" t="n">
         <v>20</v>
       </c>
       <c r="BC25" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF25" t="n">
         <v>10</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -5413,19 +5413,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="G26" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H26" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I26" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J26" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
         <v>4.1</v>
@@ -5434,38 +5434,38 @@
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N26" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="O26" t="n">
         <v>1.27</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.85</v>
       </c>
-      <c r="T26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.87</v>
-      </c>
       <c r="X26" t="n">
         <v>1000</v>
       </c>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I27" t="n">
         <v>2.92</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.78</v>
       </c>
       <c r="J27" t="n">
         <v>3.95</v>
@@ -5628,16 +5628,16 @@
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N27" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O27" t="n">
         <v>1.13</v>
       </c>
       <c r="P27" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="Q27" t="n">
         <v>1.5</v>
@@ -5655,10 +5655,10 @@
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W27" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G28" t="n">
         <v>2.4</v>
@@ -5813,10 +5813,10 @@
         <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L28" t="n">
         <v>1.23</v>
@@ -5825,46 +5825,46 @@
         <v>1.03</v>
       </c>
       <c r="N28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P28" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R28" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S28" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T28" t="n">
         <v>1.44</v>
       </c>
       <c r="U28" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V28" t="n">
         <v>1.33</v>
       </c>
       <c r="W28" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="X28" t="n">
         <v>32</v>
       </c>
       <c r="Y28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z28" t="n">
         <v>34</v>
       </c>
       <c r="AA28" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB28" t="n">
         <v>18</v>
@@ -5888,7 +5888,7 @@
         <v>18.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ28" t="n">
         <v>34</v>
@@ -5906,10 +5906,10 @@
         <v>12.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP28" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ28" t="n">
         <v>14</v>
@@ -5921,10 +5921,10 @@
         <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV28" t="n">
         <v>10.5</v>
@@ -5936,7 +5936,7 @@
         <v>12.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ28" t="n">
         <v>11</v>
@@ -5957,14 +5957,14 @@
         <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -5995,31 +5995,31 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G29" t="n">
         <v>4.6</v>
       </c>
       <c r="H29" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="I29" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="J29" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="K29" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="L29" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N29" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="O29" t="n">
         <v>1.12</v>
@@ -6043,16 +6043,16 @@
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="W29" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X29" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Y29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z29" t="n">
         <v>21</v>
@@ -6061,7 +6061,7 @@
         <v>29</v>
       </c>
       <c r="AB29" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AC29" t="n">
         <v>14</v>
@@ -6076,7 +6076,7 @@
         <v>42</v>
       </c>
       <c r="AG29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH29" t="n">
         <v>18.5</v>
@@ -6097,68 +6097,68 @@
         <v>60</v>
       </c>
       <c r="AN29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO29" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AQ29" t="n">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="AR29" t="n">
-        <v>12.5</v>
+        <v>3.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>17</v>
+        <v>3.8</v>
       </c>
       <c r="AT29" t="n">
-        <v>17</v>
+        <v>3.85</v>
       </c>
       <c r="AU29" t="n">
-        <v>8.4</v>
+        <v>3.35</v>
       </c>
       <c r="AV29" t="n">
-        <v>8.4</v>
+        <v>3.35</v>
       </c>
       <c r="AW29" t="n">
-        <v>13</v>
+        <v>3.65</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY29" t="n">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>11</v>
+        <v>3.55</v>
       </c>
       <c r="BA29" t="n">
-        <v>17.5</v>
+        <v>3.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF29" t="n">
-        <v>15.5</v>
+        <v>3.7</v>
       </c>
       <c r="BG29" t="n">
-        <v>5.7</v>
+        <v>2.96</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -6189,170 +6189,170 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="G30" t="n">
-        <v>1.66</v>
+        <v>970</v>
       </c>
       <c r="H30" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="I30" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="J30" t="n">
-        <v>3.75</v>
+        <v>1.02</v>
       </c>
       <c r="K30" t="n">
-        <v>6.2</v>
+        <v>950</v>
       </c>
       <c r="L30" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="P30" t="n">
-        <v>2.66</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="R30" t="n">
-        <v>1.71</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="T30" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y30" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AC30" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AD30" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG30" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH30" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AK30" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AL30" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>5.7</v>
+        <v>970</v>
       </c>
       <c r="AO30" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS30" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.95</v>
+        <v>1.17</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.85</v>
+        <v>1.09</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.4</v>
+        <v>1.09</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX30" t="n">
-        <v>3.85</v>
+        <v>1.26</v>
       </c>
       <c r="AY30" t="n">
-        <v>3.65</v>
+        <v>1.26</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.2</v>
+        <v>1.09</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB30" t="n">
-        <v>4</v>
+        <v>1.18</v>
       </c>
       <c r="BC30" t="n">
-        <v>3.95</v>
+        <v>1.17</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.4</v>
+        <v>1.09</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.72</v>
+        <v>1.03</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -6386,167 +6386,167 @@
         <v>1.47</v>
       </c>
       <c r="G31" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H31" t="n">
         <v>7.6</v>
       </c>
       <c r="I31" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="J31" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
         <v>4.7</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O31" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="P31" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="R31" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T31" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="U31" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="V31" t="n">
         <v>1.11</v>
       </c>
       <c r="W31" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X31" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC31" t="n">
         <v>970</v>
       </c>
-      <c r="Y31" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>12</v>
-      </c>
       <c r="AD31" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF31" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG31" t="n">
         <v>970</v>
       </c>
       <c r="AH31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ31" t="n">
         <v>970</v>
       </c>
       <c r="AK31" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AL31" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN31" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC31" t="n">
         <v>4.8</v>
       </c>
-      <c r="AU31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BD31" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BF31" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -6592,25 +6592,25 @@
         <v>2.8</v>
       </c>
       <c r="K32" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P32" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R32" t="n">
         <v>1.26</v>
@@ -6622,7 +6622,7 @@
         <v>1.73</v>
       </c>
       <c r="U32" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V32" t="n">
         <v>1.41</v>
@@ -6631,16 +6631,16 @@
         <v>1.53</v>
       </c>
       <c r="X32" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y32" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z32" t="n">
         <v>25</v>
       </c>
       <c r="AA32" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB32" t="n">
         <v>11.5</v>
@@ -6649,13 +6649,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD32" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG32" t="n">
         <v>15</v>
@@ -6679,68 +6679,68 @@
         <v>150</v>
       </c>
       <c r="AN32" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO32" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP32" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AR32" t="n">
-        <v>15</v>
+        <v>3.95</v>
       </c>
       <c r="AS32" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT32" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="AU32" t="n">
         <v>6.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="AW32" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AX32" t="n">
-        <v>12</v>
+        <v>3.85</v>
       </c>
       <c r="AY32" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AZ32" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BA32" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB32" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BC32" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BD32" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF32" t="n">
         <v>4.1</v>
       </c>
-      <c r="BF32" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BG32" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -6771,13 +6771,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="G33" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="H33" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="I33" t="n">
         <v>6.4</v>
@@ -6792,7 +6792,7 @@
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N33" t="n">
         <v>6.2</v>
@@ -6813,28 +6813,28 @@
         <v>2.08</v>
       </c>
       <c r="T33" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U33" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="V33" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W33" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X33" t="n">
         <v>40</v>
       </c>
       <c r="Y33" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z33" t="n">
         <v>60</v>
       </c>
       <c r="AA33" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB33" t="n">
         <v>17.5</v>
@@ -6846,13 +6846,13 @@
         <v>26</v>
       </c>
       <c r="AE33" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH33" t="n">
         <v>22</v>
@@ -6861,10 +6861,10 @@
         <v>60</v>
       </c>
       <c r="AJ33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK33" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL33" t="n">
         <v>32</v>
@@ -6873,22 +6873,22 @@
         <v>75</v>
       </c>
       <c r="AN33" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO33" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AQ33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT33" t="n">
         <v>10.5</v>
@@ -6897,10 +6897,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV33" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX33" t="n">
         <v>10</v>
@@ -6912,10 +6912,10 @@
         <v>12.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB33" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC33" t="n">
         <v>11</v>
@@ -6924,17 +6924,17 @@
         <v>17.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G34" t="n">
         <v>1.81</v>
@@ -6977,10 +6977,10 @@
         <v>5.6</v>
       </c>
       <c r="J34" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K34" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -7004,13 +7004,13 @@
         <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T34" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U34" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V34" t="n">
         <v>1.22</v>
@@ -7073,10 +7073,10 @@
         <v>80</v>
       </c>
       <c r="AP34" t="n">
-        <v>5.9</v>
+        <v>14</v>
       </c>
       <c r="AQ34" t="n">
-        <v>14</v>
+        <v>6.6</v>
       </c>
       <c r="AR34" t="n">
         <v>7.4</v>
@@ -7091,25 +7091,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV34" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW34" t="n">
         <v>8</v>
       </c>
       <c r="AX34" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY34" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ34" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA34" t="n">
         <v>8</v>
       </c>
       <c r="BB34" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="BC34" t="n">
         <v>16</v>
@@ -7121,14 +7121,14 @@
         <v>8.4</v>
       </c>
       <c r="BF34" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG34" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -7159,25 +7159,25 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G35" t="n">
         <v>1.82</v>
       </c>
       <c r="H35" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I35" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J35" t="n">
         <v>3.4</v>
       </c>
       <c r="K35" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M35" t="n">
         <v>1.1</v>
@@ -7195,7 +7195,7 @@
         <v>2.3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S35" t="n">
         <v>4.4</v>
@@ -7204,10 +7204,10 @@
         <v>2.12</v>
       </c>
       <c r="U35" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V35" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W35" t="n">
         <v>2.2</v>
@@ -7216,25 +7216,25 @@
         <v>12.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z35" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA35" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AB35" t="n">
         <v>8</v>
       </c>
       <c r="AC35" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD35" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE35" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF35" t="n">
         <v>11.5</v>
@@ -7243,10 +7243,10 @@
         <v>13</v>
       </c>
       <c r="AH35" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI35" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ35" t="n">
         <v>23</v>
@@ -7258,13 +7258,13 @@
         <v>65</v>
       </c>
       <c r="AM35" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN35" t="n">
         <v>20</v>
       </c>
       <c r="AO35" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AP35" t="n">
         <v>9</v>
@@ -7273,10 +7273,10 @@
         <v>11.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT35" t="n">
         <v>5.8</v>
@@ -7288,7 +7288,7 @@
         <v>17.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX35" t="n">
         <v>8.199999999999999</v>
@@ -7300,7 +7300,7 @@
         <v>18.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB35" t="n">
         <v>16.5</v>
@@ -7309,20 +7309,20 @@
         <v>19.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF35" t="n">
         <v>12</v>
       </c>
       <c r="BG35" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -7356,10 +7356,10 @@
         <v>1.86</v>
       </c>
       <c r="G36" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H36" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I36" t="n">
         <v>5.1</v>
@@ -7368,7 +7368,7 @@
         <v>3.4</v>
       </c>
       <c r="K36" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -7389,7 +7389,7 @@
         <v>1.87</v>
       </c>
       <c r="R36" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="S36" t="n">
         <v>1.87</v>
@@ -7404,7 +7404,7 @@
         <v>1.24</v>
       </c>
       <c r="W36" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -7571,13 +7571,13 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="O37" t="n">
         <v>1.3</v>
       </c>
       <c r="P37" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q37" t="n">
         <v>1.3</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7747,7 @@
         <v>2.78</v>
       </c>
       <c r="H38" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I38" t="n">
         <v>3.2</v>
@@ -7762,7 +7762,7 @@
         <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N38" t="n">
         <v>3.85</v>
@@ -7771,7 +7771,7 @@
         <v>1.3</v>
       </c>
       <c r="P38" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q38" t="n">
         <v>1.89</v>
@@ -7783,7 +7783,7 @@
         <v>3.15</v>
       </c>
       <c r="T38" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U38" t="n">
         <v>2.3</v>
@@ -7795,61 +7795,61 @@
         <v>1.56</v>
       </c>
       <c r="X38" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Y38" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z38" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA38" t="n">
         <v>60</v>
       </c>
       <c r="AB38" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC38" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD38" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AE38" t="n">
         <v>40</v>
       </c>
       <c r="AF38" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH38" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI38" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ38" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL38" t="n">
         <v>44</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>46</v>
       </c>
       <c r="AM38" t="n">
         <v>90</v>
       </c>
       <c r="AN38" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO38" t="n">
         <v>29</v>
       </c>
       <c r="AP38" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="AQ38" t="n">
         <v>10</v>
@@ -7858,10 +7858,10 @@
         <v>16</v>
       </c>
       <c r="AS38" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="AU38" t="n">
         <v>6.6</v>
@@ -7870,7 +7870,7 @@
         <v>10.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX38" t="n">
         <v>13.5</v>
@@ -7879,32 +7879,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ38" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BE38" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BF38" t="n">
         <v>16.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G39" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H39" t="n">
         <v>3.45</v>
@@ -7947,10 +7947,10 @@
         <v>4.5</v>
       </c>
       <c r="J39" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K39" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7959,16 +7959,16 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="O39" t="n">
         <v>1.35</v>
       </c>
       <c r="P39" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R39" t="n">
         <v>1.23</v>
@@ -7986,7 +7986,7 @@
         <v>1.28</v>
       </c>
       <c r="W39" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -8132,16 +8132,16 @@
         <v>1.44</v>
       </c>
       <c r="G40" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H40" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I40" t="n">
         <v>8</v>
       </c>
       <c r="J40" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K40" t="n">
         <v>5.6</v>
@@ -8156,7 +8156,7 @@
         <v>5.7</v>
       </c>
       <c r="O40" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P40" t="n">
         <v>2.66</v>
@@ -8171,7 +8171,7 @@
         <v>2.34</v>
       </c>
       <c r="T40" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U40" t="n">
         <v>2.14</v>
@@ -8231,22 +8231,22 @@
         <v>110</v>
       </c>
       <c r="AN40" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AO40" t="n">
         <v>110</v>
       </c>
       <c r="AP40" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AT40" t="n">
         <v>10</v>
@@ -8255,22 +8255,22 @@
         <v>11</v>
       </c>
       <c r="AV40" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AX40" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY40" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ40" t="n">
         <v>18.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BB40" t="n">
         <v>11.5</v>
@@ -8279,20 +8279,20 @@
         <v>12.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BF40" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -8323,16 +8323,16 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="G41" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="H41" t="n">
         <v>8.6</v>
       </c>
       <c r="I41" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="J41" t="n">
         <v>6.8</v>
@@ -8347,22 +8347,22 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="O41" t="n">
         <v>1.06</v>
       </c>
       <c r="P41" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q41" t="n">
         <v>1.29</v>
       </c>
       <c r="R41" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="S41" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="T41" t="n">
         <v>1.01</v>
@@ -8371,10 +8371,10 @@
         <v>1.01</v>
       </c>
       <c r="V41" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W41" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
         <v>2.38</v>
       </c>
       <c r="G42" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H42" t="n">
         <v>2.98</v>
@@ -8529,10 +8529,10 @@
         <v>3.7</v>
       </c>
       <c r="J42" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K42" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -8541,22 +8541,22 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O42" t="n">
         <v>1.36</v>
       </c>
       <c r="P42" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S42" t="n">
-        <v>3.2</v>
+        <v>2.02</v>
       </c>
       <c r="T42" t="n">
         <v>1.01</v>
@@ -8568,7 +8568,7 @@
         <v>1.37</v>
       </c>
       <c r="W42" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -8711,22 +8711,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="G43" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H43" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="I43" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="J43" t="n">
         <v>3.4</v>
       </c>
       <c r="K43" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
@@ -8735,22 +8735,22 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="O43" t="n">
         <v>1.01</v>
       </c>
       <c r="P43" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="R43" t="n">
         <v>1.18</v>
       </c>
       <c r="S43" t="n">
-        <v>1.73</v>
+        <v>3.15</v>
       </c>
       <c r="T43" t="n">
         <v>1.01</v>
@@ -8759,10 +8759,10 @@
         <v>1.01</v>
       </c>
       <c r="V43" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W43" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -8905,28 +8905,28 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="G44" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="H44" t="n">
         <v>1.39</v>
       </c>
       <c r="I44" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="J44" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K44" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N44" t="n">
         <v>2.34</v>
@@ -8938,13 +8938,13 @@
         <v>2.34</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="R44" t="n">
         <v>1.25</v>
       </c>
       <c r="S44" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -8953,10 +8953,10 @@
         <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="W44" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -9102,16 +9102,16 @@
         <v>1.68</v>
       </c>
       <c r="G45" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H45" t="n">
         <v>5.5</v>
       </c>
       <c r="I45" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J45" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K45" t="n">
         <v>4.3</v>
@@ -9123,146 +9123,146 @@
         <v>1.06</v>
       </c>
       <c r="N45" t="n">
-        <v>1.93</v>
+        <v>3.3</v>
       </c>
       <c r="O45" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P45" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R45" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S45" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="T45" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="U45" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="V45" t="n">
         <v>1.2</v>
       </c>
       <c r="W45" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="X45" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ45" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y45" t="n">
-        <v>27</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB45" t="n">
+      <c r="AK45" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN45" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC45" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF45" t="n">
+      <c r="AO45" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB45" t="n">
         <v>14.5</v>
       </c>
-      <c r="AG45" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN45" t="n">
+      <c r="BC45" t="n">
         <v>15.5</v>
       </c>
-      <c r="AO45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>2.52</v>
-      </c>
       <c r="BD45" t="n">
-        <v>2.64</v>
+        <v>7.6</v>
       </c>
       <c r="BE45" t="n">
-        <v>2.78</v>
+        <v>9</v>
       </c>
       <c r="BF45" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BG45" t="n">
-        <v>2.78</v>
+        <v>8.4</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
         <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H46" t="n">
         <v>3.4</v>
@@ -9314,16 +9314,16 @@
         <v>1.01</v>
       </c>
       <c r="M46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N46" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="O46" t="n">
         <v>1.16</v>
       </c>
       <c r="P46" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q46" t="n">
         <v>1.48</v>
@@ -9344,7 +9344,7 @@
         <v>1.29</v>
       </c>
       <c r="W46" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -9681,22 +9681,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G48" t="n">
         <v>4.5</v>
       </c>
       <c r="H48" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I48" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="J48" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K48" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
@@ -9705,31 +9705,31 @@
         <v>1.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="O48" t="n">
         <v>1.44</v>
       </c>
       <c r="P48" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R48" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S48" t="n">
         <v>4.4</v>
       </c>
       <c r="T48" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U48" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V48" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W48" t="n">
         <v>1.28</v>
@@ -9738,13 +9738,13 @@
         <v>12</v>
       </c>
       <c r="Y48" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z48" t="n">
         <v>14.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB48" t="n">
         <v>14.5</v>
@@ -9762,16 +9762,16 @@
         <v>34</v>
       </c>
       <c r="AG48" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH48" t="n">
         <v>25</v>
       </c>
       <c r="AI48" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ48" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK48" t="n">
         <v>75</v>
@@ -9780,28 +9780,28 @@
         <v>90</v>
       </c>
       <c r="AM48" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN48" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO48" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP48" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ48" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR48" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AS48" t="n">
-        <v>21</v>
+        <v>4.5</v>
       </c>
       <c r="AT48" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AU48" t="n">
         <v>6.6</v>
@@ -9810,41 +9810,41 @@
         <v>9.6</v>
       </c>
       <c r="AW48" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="AX48" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY48" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AZ48" t="n">
         <v>18.5</v>
       </c>
       <c r="BA48" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB48" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC48" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BD48" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE48" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF48" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF48" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG48" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -9875,22 +9875,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G49" t="n">
         <v>4.4</v>
       </c>
       <c r="H49" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="I49" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="J49" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="K49" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
@@ -9899,52 +9899,52 @@
         <v>1.03</v>
       </c>
       <c r="N49" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="O49" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P49" t="n">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="Q49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T49" t="n">
         <v>1.58</v>
       </c>
-      <c r="R49" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T49" t="n">
-        <v>1.54</v>
-      </c>
       <c r="U49" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="V49" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="W49" t="n">
         <v>1.29</v>
       </c>
       <c r="X49" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y49" t="n">
         <v>14.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA49" t="n">
         <v>23</v>
       </c>
       <c r="AB49" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AC49" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD49" t="n">
         <v>13</v>
@@ -9953,7 +9953,7 @@
         <v>19.5</v>
       </c>
       <c r="AF49" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG49" t="n">
         <v>21</v>
@@ -9977,13 +9977,13 @@
         <v>60</v>
       </c>
       <c r="AN49" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO49" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP49" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="AQ49" t="n">
         <v>11.5</v>
@@ -9995,10 +9995,10 @@
         <v>18</v>
       </c>
       <c r="AT49" t="n">
-        <v>18</v>
+        <v>5.5</v>
       </c>
       <c r="AU49" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV49" t="n">
         <v>9.4</v>
@@ -10007,7 +10007,7 @@
         <v>14.5</v>
       </c>
       <c r="AX49" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY49" t="n">
         <v>15</v>
@@ -10019,26 +10019,26 @@
         <v>21</v>
       </c>
       <c r="BB49" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC49" t="n">
         <v>34</v>
       </c>
       <c r="BD49" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE49" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF49" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BG49" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -10069,22 +10069,22 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G50" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H50" t="n">
-        <v>5.7</v>
+        <v>2.84</v>
       </c>
       <c r="I50" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="J50" t="n">
-        <v>4.8</v>
+        <v>2.82</v>
       </c>
       <c r="K50" t="n">
-        <v>5.7</v>
+        <v>80</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
@@ -10093,146 +10093,146 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>3.45</v>
+        <v>1.26</v>
       </c>
       <c r="O50" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P50" t="n">
-        <v>2.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.51</v>
+        <v>1.15</v>
       </c>
       <c r="R50" t="n">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="S50" t="n">
-        <v>2.06</v>
+        <v>1.15</v>
       </c>
       <c r="T50" t="n">
-        <v>1.68</v>
+        <v>1.05</v>
       </c>
       <c r="U50" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W50" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="X50" t="n">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="Y50" t="n">
+        <v>130</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>490</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>290</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF50" t="n">
         <v>36</v>
       </c>
-      <c r="Z50" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>260</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>46</v>
-      </c>
-      <c r="AC50" t="n">
+      <c r="AG50" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>340</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>680</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AZ50" t="n">
         <v>13</v>
       </c>
-      <c r="AD50" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>330</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BA50" t="n">
-        <v>4.6</v>
+        <v>1.24</v>
       </c>
       <c r="BB50" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="BC50" t="n">
         <v>12</v>
       </c>
       <c r="BD50" t="n">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="BE50" t="n">
-        <v>4.6</v>
+        <v>1.24</v>
       </c>
       <c r="BF50" t="n">
-        <v>3.7</v>
+        <v>2.06</v>
       </c>
       <c r="BG50" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>2.24</v>
       </c>
       <c r="G51" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H51" t="n">
         <v>2.94</v>
@@ -10281,34 +10281,34 @@
         <v>4.2</v>
       </c>
       <c r="L51" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M51" t="n">
         <v>1.03</v>
       </c>
       <c r="N51" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O51" t="n">
         <v>1.16</v>
       </c>
       <c r="P51" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R51" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="S51" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T51" t="n">
         <v>1.49</v>
       </c>
       <c r="U51" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="V51" t="n">
         <v>1.46</v>
@@ -10359,10 +10359,10 @@
         <v>21</v>
       </c>
       <c r="AL51" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM51" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AN51" t="n">
         <v>12</v>
@@ -10374,13 +10374,13 @@
         <v>7.2</v>
       </c>
       <c r="AQ51" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR51" t="n">
         <v>7</v>
       </c>
       <c r="AS51" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT51" t="n">
         <v>15</v>
@@ -10392,7 +10392,7 @@
         <v>12.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX51" t="n">
         <v>6.4</v>
@@ -10401,16 +10401,16 @@
         <v>10.5</v>
       </c>
       <c r="AZ51" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BA51" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB51" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC51" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD51" t="n">
         <v>7</v>
@@ -10419,14 +10419,14 @@
         <v>8</v>
       </c>
       <c r="BF51" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG51" t="n">
         <v>12</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -10457,16 +10457,16 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G52" t="n">
         <v>2.82</v>
       </c>
       <c r="H52" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I52" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="J52" t="n">
         <v>3.1</v>
@@ -10481,16 +10481,16 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="O52" t="n">
         <v>1.38</v>
       </c>
       <c r="P52" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R52" t="n">
         <v>1.21</v>
@@ -10505,7 +10505,7 @@
         <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W52" t="n">
         <v>1.54</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -11039,10 +11039,10 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="G55" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H55" t="n">
         <v>2.66</v>
@@ -11054,7 +11054,7 @@
         <v>3.35</v>
       </c>
       <c r="K55" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L55" t="n">
         <v>1.01</v>
@@ -11063,28 +11063,28 @@
         <v>1.06</v>
       </c>
       <c r="N55" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O55" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P55" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="R55" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S55" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="T55" t="n">
         <v>1.46</v>
       </c>
       <c r="U55" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V55" t="n">
         <v>1.47</v>
@@ -11096,7 +11096,7 @@
         <v>20</v>
       </c>
       <c r="Y55" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z55" t="n">
         <v>25</v>
@@ -11144,13 +11144,13 @@
         <v>26</v>
       </c>
       <c r="AO55" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP55" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ55" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR55" t="n">
         <v>14.5</v>
@@ -11189,20 +11189,20 @@
         <v>20</v>
       </c>
       <c r="BD55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE55" t="n">
         <v>1.01</v>
       </c>
       <c r="BF55" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG55" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -11427,16 +11427,16 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="G57" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H57" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="I57" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="J57" t="n">
         <v>4.5</v>
@@ -11466,28 +11466,28 @@
         <v>1.53</v>
       </c>
       <c r="S57" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T57" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U57" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V57" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="W57" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X57" t="n">
         <v>27</v>
       </c>
       <c r="Y57" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z57" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA57" t="n">
         <v>17</v>
@@ -11505,7 +11505,7 @@
         <v>18.5</v>
       </c>
       <c r="AF57" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AG57" t="n">
         <v>32</v>
@@ -11559,7 +11559,7 @@
         <v>11</v>
       </c>
       <c r="AX57" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AY57" t="n">
         <v>18.5</v>
@@ -11568,29 +11568,29 @@
         <v>18.5</v>
       </c>
       <c r="BA57" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BB57" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD57" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC57" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BE57" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF57" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BG57" t="n">
         <v>5</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -11621,22 +11621,22 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="G58" t="n">
         <v>3.4</v>
       </c>
       <c r="H58" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I58" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="J58" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K58" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
@@ -11645,13 +11645,13 @@
         <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="O58" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P58" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q58" t="n">
         <v>1.85</v>
@@ -11669,7 +11669,7 @@
         <v>1.01</v>
       </c>
       <c r="V58" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W58" t="n">
         <v>1.44</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -11818,19 +11818,19 @@
         <v>2.26</v>
       </c>
       <c r="G59" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="H59" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="J59" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="K59" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="L59" t="n">
         <v>1.01</v>
@@ -11863,10 +11863,10 @@
         <v>1.01</v>
       </c>
       <c r="V59" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W59" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="X59" t="n">
         <v>1000</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12009,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G60" t="n">
         <v>2.1</v>
@@ -12024,13 +12024,13 @@
         <v>3.35</v>
       </c>
       <c r="K60" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L60" t="n">
         <v>1.01</v>
       </c>
       <c r="M60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N60" t="n">
         <v>2.08</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -12227,16 +12227,16 @@
         <v>1.01</v>
       </c>
       <c r="N61" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="O61" t="n">
         <v>1.11</v>
       </c>
       <c r="P61" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R61" t="n">
         <v>1.65</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -12427,10 +12427,10 @@
         <v>1.4</v>
       </c>
       <c r="P62" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q62" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R62" t="n">
         <v>1.23</v>
@@ -12469,7 +12469,7 @@
         <v>10.5</v>
       </c>
       <c r="AD62" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE62" t="n">
         <v>75</v>
@@ -12487,7 +12487,7 @@
         <v>95</v>
       </c>
       <c r="AJ62" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK62" t="n">
         <v>40</v>
@@ -12514,7 +12514,7 @@
         <v>2.36</v>
       </c>
       <c r="AS62" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AT62" t="n">
         <v>2.06</v>
@@ -12526,19 +12526,19 @@
         <v>2.26</v>
       </c>
       <c r="AW62" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AX62" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AY62" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AZ62" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BA62" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BB62" t="n">
         <v>2.38</v>
@@ -12547,20 +12547,20 @@
         <v>2.36</v>
       </c>
       <c r="BD62" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BE62" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BF62" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BG62" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -12591,7 +12591,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G63" t="n">
         <v>5</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -12797,7 +12797,7 @@
         <v>3.5</v>
       </c>
       <c r="J64" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K64" t="n">
         <v>3.9</v>
@@ -12809,7 +12809,7 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="O64" t="n">
         <v>1.29</v>
@@ -12818,7 +12818,7 @@
         <v>1.97</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="R64" t="n">
         <v>1.3</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -12979,19 +12979,19 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G65" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="H65" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="I65" t="n">
         <v>8</v>
       </c>
       <c r="J65" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="K65" t="n">
         <v>5.1</v>
@@ -13012,7 +13012,7 @@
         <v>2.28</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R65" t="n">
         <v>1.35</v>
@@ -13030,7 +13030,7 @@
         <v>1.14</v>
       </c>
       <c r="W65" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="X65" t="n">
         <v>1000</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -13173,22 +13173,22 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="G66" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="H66" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="I66" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="J66" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="K66" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="L66" t="n">
         <v>1.01</v>
@@ -13200,13 +13200,13 @@
         <v>1.25</v>
       </c>
       <c r="O66" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P66" t="n">
         <v>1.25</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R66" t="n">
         <v>1.24</v>
@@ -13221,122 +13221,122 @@
         <v>1.01</v>
       </c>
       <c r="V66" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="W66" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="X66" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="Y66" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="Z66" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AA66" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB66" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AC66" t="n">
         <v>970</v>
       </c>
       <c r="AD66" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE66" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF66" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AG66" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AH66" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AI66" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ66" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK66" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL66" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM66" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN66" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO66" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS66" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AU66" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AV66" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW66" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AX66" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AY66" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ66" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA66" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="BB66" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="BC66" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="BD66" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="BE66" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="BF66" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG66" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -13373,7 +13373,7 @@
         <v>2.54</v>
       </c>
       <c r="H67" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="I67" t="n">
         <v>4.1</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -13561,7 +13561,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G68" t="n">
         <v>3.2</v>
@@ -13570,10 +13570,10 @@
         <v>2.42</v>
       </c>
       <c r="I68" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="J68" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K68" t="n">
         <v>3.7</v>
@@ -13582,22 +13582,22 @@
         <v>1.01</v>
       </c>
       <c r="M68" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N68" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O68" t="n">
         <v>1.3</v>
       </c>
       <c r="P68" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R68" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S68" t="n">
         <v>3.15</v>
@@ -13609,28 +13609,28 @@
         <v>2.16</v>
       </c>
       <c r="V68" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="W68" t="n">
         <v>1.45</v>
       </c>
       <c r="X68" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y68" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z68" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA68" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB68" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC68" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD68" t="n">
         <v>13.5</v>
@@ -13669,16 +13669,16 @@
         <v>24</v>
       </c>
       <c r="AP68" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ68" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR68" t="n">
         <v>13</v>
       </c>
       <c r="AS68" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT68" t="n">
         <v>10</v>
@@ -13693,38 +13693,38 @@
         <v>20</v>
       </c>
       <c r="AX68" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AY68" t="n">
         <v>10</v>
       </c>
       <c r="AZ68" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BA68" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BB68" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF68" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BC68" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD68" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE68" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF68" t="n">
-        <v>4.5</v>
       </c>
       <c r="BG68" t="n">
         <v>15.5</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
         <v>1.13</v>
       </c>
       <c r="N69" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O69" t="n">
         <v>1.53</v>
@@ -13815,7 +13815,7 @@
         <v>7.8</v>
       </c>
       <c r="Z69" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA69" t="n">
         <v>38</v>
@@ -13851,7 +13851,7 @@
         <v>50</v>
       </c>
       <c r="AL69" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM69" t="n">
         <v>170</v>
@@ -13884,7 +13884,7 @@
         <v>11.5</v>
       </c>
       <c r="AW69" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX69" t="n">
         <v>19</v>
@@ -13905,7 +13905,7 @@
         <v>44</v>
       </c>
       <c r="BD69" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BE69" t="n">
         <v>46</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -13958,13 +13958,13 @@
         <v>2.68</v>
       </c>
       <c r="I70" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="J70" t="n">
         <v>3.5</v>
       </c>
       <c r="K70" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L70" t="n">
         <v>1.01</v>
@@ -13979,25 +13979,25 @@
         <v>1.27</v>
       </c>
       <c r="P70" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q70" t="n">
         <v>1.85</v>
       </c>
       <c r="R70" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S70" t="n">
         <v>2.84</v>
       </c>
       <c r="T70" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U70" t="n">
         <v>1.84</v>
       </c>
       <c r="V70" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W70" t="n">
         <v>1.55</v>
@@ -14015,7 +14015,7 @@
         <v>60</v>
       </c>
       <c r="AB70" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC70" t="n">
         <v>12</v>
@@ -14039,7 +14039,7 @@
         <v>55</v>
       </c>
       <c r="AJ70" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK70" t="n">
         <v>44</v>
@@ -14057,13 +14057,13 @@
         <v>1000</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AS70" t="n">
         <v>2.06</v>
@@ -14072,25 +14072,25 @@
         <v>1.91</v>
       </c>
       <c r="AU70" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AV70" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AW70" t="n">
         <v>2.04</v>
       </c>
       <c r="AX70" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AY70" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AZ70" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="BA70" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BB70" t="n">
         <v>2.06</v>
@@ -14099,20 +14099,20 @@
         <v>2.04</v>
       </c>
       <c r="BD70" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BE70" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BF70" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BG70" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -14143,10 +14143,10 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G71" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H71" t="n">
         <v>1.77</v>
@@ -14158,46 +14158,46 @@
         <v>3.75</v>
       </c>
       <c r="K71" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L71" t="n">
         <v>1.01</v>
       </c>
       <c r="M71" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N71" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="O71" t="n">
         <v>1.26</v>
       </c>
       <c r="P71" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R71" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S71" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T71" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="U71" t="n">
         <v>2.12</v>
       </c>
       <c r="V71" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W71" t="n">
         <v>1.24</v>
       </c>
       <c r="X71" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y71" t="n">
         <v>970</v>
@@ -14209,7 +14209,7 @@
         <v>24</v>
       </c>
       <c r="AB71" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC71" t="n">
         <v>970</v>
@@ -14227,7 +14227,7 @@
         <v>24</v>
       </c>
       <c r="AH71" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI71" t="n">
         <v>1000</v>
@@ -14251,62 +14251,62 @@
         <v>970</v>
       </c>
       <c r="AP71" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AQ71" t="n">
-        <v>6.8</v>
+        <v>1.97</v>
       </c>
       <c r="AR71" t="n">
-        <v>8.199999999999999</v>
+        <v>2.02</v>
       </c>
       <c r="AS71" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="AT71" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="AU71" t="n">
-        <v>6.6</v>
+        <v>1.96</v>
       </c>
       <c r="AV71" t="n">
-        <v>6.6</v>
+        <v>1.96</v>
       </c>
       <c r="AW71" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="AX71" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="AY71" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="AZ71" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="BA71" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="BB71" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="BC71" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="BD71" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="BE71" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="BF71" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="BG71" t="n">
-        <v>7.2</v>
+        <v>2</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -14337,22 +14337,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="G72" t="n">
         <v>5.4</v>
       </c>
       <c r="H72" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="I72" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J72" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K72" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="L72" t="n">
         <v>1.35</v>
@@ -14361,16 +14361,16 @@
         <v>1.01</v>
       </c>
       <c r="N72" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="O72" t="n">
         <v>1.36</v>
       </c>
       <c r="P72" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R72" t="n">
         <v>1.22</v>
@@ -14385,7 +14385,7 @@
         <v>1.69</v>
       </c>
       <c r="V72" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="W72" t="n">
         <v>1.23</v>
@@ -14403,7 +14403,7 @@
         <v>30</v>
       </c>
       <c r="AB72" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC72" t="n">
         <v>10.5</v>
@@ -14430,10 +14430,10 @@
         <v>1000</v>
       </c>
       <c r="AK72" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL72" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM72" t="n">
         <v>1000</v>
@@ -14454,19 +14454,19 @@
         <v>9</v>
       </c>
       <c r="AS72" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AT72" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU72" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AV72" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AW72" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AX72" t="n">
         <v>23</v>
@@ -14475,32 +14475,32 @@
         <v>13.5</v>
       </c>
       <c r="AZ72" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BA72" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BB72" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BC72" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BD72" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BE72" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BF72" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BG72" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
         <v>4.6</v>
       </c>
       <c r="I73" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J73" t="n">
         <v>3.55</v>
@@ -14555,13 +14555,13 @@
         <v>1.01</v>
       </c>
       <c r="N73" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O73" t="n">
         <v>1.31</v>
       </c>
       <c r="P73" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q73" t="n">
         <v>1.99</v>
@@ -14579,7 +14579,7 @@
         <v>1.01</v>
       </c>
       <c r="V73" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W73" t="n">
         <v>2.04</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -14725,16 +14725,16 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="G74" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="H74" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="I74" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J74" t="n">
         <v>3.1</v>
@@ -14749,13 +14749,13 @@
         <v>1.01</v>
       </c>
       <c r="N74" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O74" t="n">
         <v>1.38</v>
       </c>
       <c r="P74" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q74" t="n">
         <v>2.1</v>
@@ -14773,10 +14773,10 @@
         <v>1.01</v>
       </c>
       <c r="V74" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W74" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X74" t="n">
         <v>1000</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -14919,10 +14919,10 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="G75" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H75" t="n">
         <v>5.7</v>
@@ -14934,7 +14934,7 @@
         <v>4.2</v>
       </c>
       <c r="K75" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="L75" t="n">
         <v>1.01</v>
@@ -14970,7 +14970,7 @@
         <v>1.09</v>
       </c>
       <c r="W75" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X75" t="n">
         <v>1000</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -15113,19 +15113,19 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="G76" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="H76" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I76" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J76" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K76" t="n">
         <v>4.2</v>
@@ -15137,16 +15137,16 @@
         <v>1.01</v>
       </c>
       <c r="N76" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="O76" t="n">
         <v>1.27</v>
       </c>
       <c r="P76" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R76" t="n">
         <v>1.3</v>
@@ -15161,10 +15161,10 @@
         <v>1.01</v>
       </c>
       <c r="V76" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W76" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="X76" t="n">
         <v>1000</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -15501,19 +15501,19 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="G78" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H78" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I78" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J78" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K78" t="n">
         <v>3.85</v>
@@ -15525,19 +15525,19 @@
         <v>1.01</v>
       </c>
       <c r="N78" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="O78" t="n">
         <v>1.35</v>
       </c>
       <c r="P78" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="R78" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S78" t="n">
         <v>3.3</v>
@@ -15552,7 +15552,7 @@
         <v>1.27</v>
       </c>
       <c r="W78" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X78" t="n">
         <v>1000</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -15698,13 +15698,13 @@
         <v>2.38</v>
       </c>
       <c r="G79" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H79" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I79" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J79" t="n">
         <v>3.25</v>
@@ -15719,25 +15719,25 @@
         <v>1.01</v>
       </c>
       <c r="N79" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="O79" t="n">
         <v>1.02</v>
       </c>
       <c r="P79" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q79" t="n">
         <v>2.18</v>
       </c>
       <c r="R79" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S79" t="n">
         <v>3.55</v>
       </c>
       <c r="T79" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U79" t="n">
         <v>1.75</v>
@@ -15746,10 +15746,10 @@
         <v>1.37</v>
       </c>
       <c r="W79" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X79" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y79" t="n">
         <v>17</v>
@@ -15761,7 +15761,7 @@
         <v>95</v>
       </c>
       <c r="AB79" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC79" t="n">
         <v>10.5</v>
@@ -15773,10 +15773,10 @@
         <v>65</v>
       </c>
       <c r="AF79" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG79" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH79" t="n">
         <v>28</v>
@@ -15785,7 +15785,7 @@
         <v>85</v>
       </c>
       <c r="AJ79" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK79" t="n">
         <v>44</v>
@@ -15803,7 +15803,7 @@
         <v>1000</v>
       </c>
       <c r="AP79" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AQ79" t="n">
         <v>9.199999999999999</v>
@@ -15812,10 +15812,10 @@
         <v>18</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AT79" t="n">
-        <v>7.4</v>
+        <v>2.12</v>
       </c>
       <c r="AU79" t="n">
         <v>6</v>
@@ -15824,41 +15824,41 @@
         <v>12</v>
       </c>
       <c r="AW79" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AX79" t="n">
         <v>10</v>
       </c>
       <c r="AY79" t="n">
-        <v>9.6</v>
+        <v>2.22</v>
       </c>
       <c r="AZ79" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="BA79" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BC79" t="n">
         <v>2.42</v>
       </c>
-      <c r="BB79" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BC79" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BD79" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BE79" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="BF79" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="BG79" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -15898,7 +15898,7 @@
         <v>3.85</v>
       </c>
       <c r="I80" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J80" t="n">
         <v>3.65</v>
@@ -15919,10 +15919,10 @@
         <v>1.29</v>
       </c>
       <c r="P80" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R80" t="n">
         <v>1.42</v>
@@ -15946,7 +15946,7 @@
         <v>15</v>
       </c>
       <c r="Y80" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z80" t="n">
         <v>28</v>
@@ -15976,7 +15976,7 @@
         <v>17</v>
       </c>
       <c r="AI80" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ80" t="n">
         <v>25</v>
@@ -15997,19 +15997,19 @@
         <v>40</v>
       </c>
       <c r="AP80" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ80" t="n">
         <v>14.5</v>
       </c>
       <c r="AR80" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS80" t="n">
         <v>34</v>
       </c>
       <c r="AT80" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU80" t="n">
         <v>7.6</v>
@@ -16030,7 +16030,7 @@
         <v>15.5</v>
       </c>
       <c r="BA80" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="BB80" t="n">
         <v>23</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -16083,7 +16083,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="G81" t="n">
         <v>1.31</v>
@@ -16092,7 +16092,7 @@
         <v>13</v>
       </c>
       <c r="I81" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
         <v>6</v>
@@ -16107,16 +16107,16 @@
         <v>1.01</v>
       </c>
       <c r="N81" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="O81" t="n">
         <v>1.16</v>
       </c>
       <c r="P81" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="R81" t="n">
         <v>1.51</v>
@@ -16128,7 +16128,7 @@
         <v>1.75</v>
       </c>
       <c r="U81" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V81" t="n">
         <v>1.06</v>
@@ -16155,7 +16155,7 @@
         <v>22</v>
       </c>
       <c r="AD81" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AE81" t="n">
         <v>1000</v>
@@ -16167,7 +16167,7 @@
         <v>17</v>
       </c>
       <c r="AH81" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AI81" t="n">
         <v>1000</v>
@@ -16179,7 +16179,7 @@
         <v>21</v>
       </c>
       <c r="AL81" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM81" t="n">
         <v>1000</v>
@@ -16191,62 +16191,62 @@
         <v>1000</v>
       </c>
       <c r="AP81" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AQ81" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AR81" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AS81" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AT81" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AU81" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AV81" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AW81" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AX81" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AY81" t="n">
         <v>2.34</v>
       </c>
       <c r="AZ81" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BA81" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BB81" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BC81" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BD81" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BE81" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BF81" t="n">
         <v>2.96</v>
       </c>
       <c r="BG81" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16322,7 @@
         <v>2</v>
       </c>
       <c r="U82" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V82" t="n">
         <v>1.13</v>
@@ -16385,13 +16385,13 @@
         <v>140</v>
       </c>
       <c r="AP82" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ82" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR82" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AS82" t="n">
         <v>75</v>
@@ -16418,7 +16418,7 @@
         <v>23</v>
       </c>
       <c r="BA82" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="BB82" t="n">
         <v>11.5</v>
@@ -16427,7 +16427,7 @@
         <v>13.5</v>
       </c>
       <c r="BD82" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE82" t="n">
         <v>60</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -16668,16 +16668,16 @@
         <v>1.95</v>
       </c>
       <c r="G84" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H84" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I84" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J84" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K84" t="n">
         <v>3.7</v>
@@ -16695,19 +16695,19 @@
         <v>1.4</v>
       </c>
       <c r="P84" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R84" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S84" t="n">
         <v>3.75</v>
       </c>
       <c r="T84" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U84" t="n">
         <v>1.58</v>
@@ -16716,7 +16716,7 @@
         <v>1.25</v>
       </c>
       <c r="W84" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X84" t="n">
         <v>16</v>
@@ -16725,13 +16725,13 @@
         <v>20</v>
       </c>
       <c r="Z84" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA84" t="n">
         <v>1000</v>
       </c>
       <c r="AB84" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC84" t="n">
         <v>11.5</v>
@@ -16740,10 +16740,10 @@
         <v>28</v>
       </c>
       <c r="AE84" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF84" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG84" t="n">
         <v>15.5</v>
@@ -16773,31 +16773,31 @@
         <v>1000</v>
       </c>
       <c r="AP84" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AQ84" t="n">
         <v>2.12</v>
       </c>
       <c r="AR84" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AS84" t="n">
         <v>2.38</v>
       </c>
       <c r="AT84" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AU84" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AV84" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AW84" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AX84" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AY84" t="n">
         <v>2.06</v>
@@ -16812,7 +16812,7 @@
         <v>2.22</v>
       </c>
       <c r="BC84" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BD84" t="n">
         <v>2.3</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -17247,22 +17247,22 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="G87" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="H87" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="I87" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="J87" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K87" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="L87" t="n">
         <v>1.01</v>
@@ -17271,22 +17271,22 @@
         <v>1.01</v>
       </c>
       <c r="N87" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="O87" t="n">
         <v>1.14</v>
       </c>
       <c r="P87" t="n">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="Q87" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="R87" t="n">
         <v>1.53</v>
       </c>
       <c r="S87" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="T87" t="n">
         <v>1.01</v>
@@ -17295,10 +17295,10 @@
         <v>1.01</v>
       </c>
       <c r="V87" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="W87" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="X87" t="n">
         <v>1000</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -17441,22 +17441,22 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="G88" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="H88" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="I88" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="J88" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K88" t="n">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="L88" t="n">
         <v>1.01</v>
@@ -17489,10 +17489,10 @@
         <v>1.01</v>
       </c>
       <c r="V88" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W88" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="X88" t="n">
         <v>1000</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -17829,22 +17829,22 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="G90" t="n">
-        <v>970</v>
+        <v>3.3</v>
       </c>
       <c r="H90" t="n">
         <v>2.8</v>
       </c>
       <c r="I90" t="n">
-        <v>970</v>
+        <v>3.9</v>
       </c>
       <c r="J90" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="K90" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L90" t="n">
         <v>1.01</v>
@@ -17862,13 +17862,13 @@
         <v>1.81</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="R90" t="n">
         <v>1.18</v>
       </c>
       <c r="S90" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="T90" t="n">
         <v>1.01</v>
@@ -17877,7 +17877,7 @@
         <v>1.01</v>
       </c>
       <c r="V90" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W90" t="n">
         <v>1.44</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -18217,22 +18217,22 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="G92" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="H92" t="n">
         <v>2.46</v>
       </c>
       <c r="I92" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="J92" t="n">
-        <v>3.15</v>
+        <v>2.26</v>
       </c>
       <c r="K92" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="L92" t="n">
         <v>1.01</v>
@@ -18241,82 +18241,82 @@
         <v>1.01</v>
       </c>
       <c r="N92" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="O92" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="P92" t="n">
-        <v>1.9</v>
+        <v>1.33</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="R92" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S92" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="T92" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="U92" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V92" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="W92" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="X92" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y92" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z92" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA92" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB92" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC92" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD92" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE92" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF92" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG92" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AH92" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI92" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ92" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK92" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL92" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM92" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN92" t="n">
         <v>1000</v>
@@ -18325,62 +18325,62 @@
         <v>1000</v>
       </c>
       <c r="AP92" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="AQ92" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AR92" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS92" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT92" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU92" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="AV92" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="AW92" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX92" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY92" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ92" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BA92" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB92" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BC92" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD92" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BE92" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BF92" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="BG92" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -18411,22 +18411,22 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="G93" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H93" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I93" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="J93" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K93" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L93" t="n">
         <v>1.01</v>
@@ -18435,16 +18435,16 @@
         <v>1.01</v>
       </c>
       <c r="N93" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O93" t="n">
         <v>1.41</v>
       </c>
       <c r="P93" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R93" t="n">
         <v>1.2</v>
@@ -18459,10 +18459,10 @@
         <v>1.01</v>
       </c>
       <c r="V93" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W93" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X93" t="n">
         <v>1000</v>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="80">
   <si>
     <t>League</t>
   </si>
@@ -199,27 +199,18 @@
     <t>Bolivian Liga de Futbol Profesional</t>
   </si>
   <si>
-    <t>English Premier League</t>
-  </si>
-  <si>
-    <t>Icelandic 1 Deild</t>
-  </si>
-  <si>
     <t>Ecuadorian Serie A</t>
   </si>
   <si>
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
     <t>2026-05-01</t>
   </si>
   <si>
-    <t>16:00:00</t>
-  </si>
-  <si>
-    <t>16:15:00</t>
-  </si>
-  <si>
     <t>18:15:00</t>
   </si>
   <si>
@@ -232,21 +223,6 @@
     <t>21:00:00</t>
   </si>
   <si>
-    <t>San Antonio Bulo Bulo</t>
-  </si>
-  <si>
-    <t>Leeds</t>
-  </si>
-  <si>
-    <t>HK Kopavogur</t>
-  </si>
-  <si>
-    <t>Throttur</t>
-  </si>
-  <si>
-    <t>Grotta</t>
-  </si>
-  <si>
     <t>Real Potosi</t>
   </si>
   <si>
@@ -256,24 +232,12 @@
     <t>Once Caldas</t>
   </si>
   <si>
+    <t>Libertad</t>
+  </si>
+  <si>
     <t>Libertad FC</t>
   </si>
   <si>
-    <t>Club Independiente Petrol</t>
-  </si>
-  <si>
-    <t>Burnley</t>
-  </si>
-  <si>
-    <t>Aegir</t>
-  </si>
-  <si>
-    <t>IR Reykjavik</t>
-  </si>
-  <si>
-    <t>Leiknir R</t>
-  </si>
-  <si>
     <t>CDT Real Oruro</t>
   </si>
   <si>
@@ -283,10 +247,13 @@
     <t>Atletico Nacional Medellin</t>
   </si>
   <si>
+    <t>Sportivo San Lorenzo</t>
+  </si>
+  <si>
     <t>Aucas</t>
   </si>
   <si>
-    <t>2026-05-01 18:06:46</t>
+    <t>2026-05-01 20:37:23</t>
   </si>
 </sst>
 </file>
@@ -644,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BH6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:60">
@@ -834,34 +801,34 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" t="s">
         <v>65</v>
       </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F2">
-        <v>1.24</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1.27</v>
+        <v>1000</v>
       </c>
       <c r="H2">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="I2">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="J2">
-        <v>5.5</v>
+        <v>50</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -876,28 +843,28 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="R2">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="S2">
-        <v>1.74</v>
+        <v>34</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.02</v>
+        <v>95</v>
       </c>
       <c r="W2">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -906,7 +873,7 @@
         <v>1000</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>1.17</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -927,88 +894,88 @@
         <v>1000</v>
       </c>
       <c r="AG2">
-        <v>2.18</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>11</v>
+      </c>
+      <c r="AQ2">
+        <v>6.6</v>
+      </c>
+      <c r="AR2">
+        <v>1.04</v>
+      </c>
+      <c r="AS2">
         <v>7.4</v>
       </c>
-      <c r="AI2">
-        <v>65</v>
-      </c>
-      <c r="AJ2">
-        <v>1000</v>
-      </c>
-      <c r="AK2">
-        <v>5.4</v>
-      </c>
-      <c r="AL2">
-        <v>23</v>
-      </c>
-      <c r="AM2">
-        <v>190</v>
-      </c>
-      <c r="AN2">
-        <v>26</v>
-      </c>
-      <c r="AO2">
-        <v>1000</v>
-      </c>
-      <c r="AP2">
-        <v>8</v>
-      </c>
-      <c r="AQ2">
-        <v>8</v>
-      </c>
-      <c r="AR2">
-        <v>8</v>
-      </c>
-      <c r="AS2">
-        <v>8</v>
-      </c>
       <c r="AT2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AU2">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AW2">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AX2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AY2">
-        <v>2.04</v>
+        <v>6.6</v>
       </c>
       <c r="AZ2">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BA2">
-        <v>34</v>
+        <v>6.6</v>
       </c>
       <c r="BB2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BC2">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BD2">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="BE2">
-        <v>70</v>
+        <v>6.6</v>
       </c>
       <c r="BF2">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG2">
-        <v>190</v>
+        <v>7.6</v>
       </c>
       <c r="BH2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -1016,34 +983,34 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
         <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F3">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="H3">
-        <v>1000</v>
+        <v>1.28</v>
       </c>
       <c r="I3">
-        <v>1000</v>
+        <v>1.29</v>
       </c>
       <c r="J3">
-        <v>400</v>
+        <v>4.8</v>
       </c>
       <c r="K3">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1076,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="V3">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="W3">
-        <v>280</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1115,82 +1082,82 @@
         <v>1000</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>1.69</v>
       </c>
       <c r="AJ3">
         <v>1000</v>
       </c>
       <c r="AK3">
-        <v>1.24</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="AN3">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AP3">
         <v>1000</v>
       </c>
       <c r="AQ3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AR3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AS3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AT3">
         <v>1000</v>
       </c>
       <c r="AU3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AV3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AW3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AX3">
         <v>1000</v>
       </c>
       <c r="AY3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AZ3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BA3">
-        <v>1000</v>
+        <v>1.53</v>
       </c>
       <c r="BB3">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BC3">
-        <v>1.23</v>
+        <v>110</v>
       </c>
       <c r="BD3">
-        <v>11.5</v>
+        <v>110</v>
       </c>
       <c r="BE3">
-        <v>100</v>
+        <v>3.5</v>
       </c>
       <c r="BF3">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BG3">
-        <v>150</v>
+        <v>2.54</v>
       </c>
       <c r="BH3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -1198,216 +1165,216 @@
         <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
         <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F4">
-        <v>1.05</v>
+        <v>2.74</v>
       </c>
       <c r="G4">
+        <v>2.76</v>
+      </c>
+      <c r="H4">
+        <v>2.78</v>
+      </c>
+      <c r="I4">
+        <v>2.82</v>
+      </c>
+      <c r="J4">
+        <v>3.5</v>
+      </c>
+      <c r="K4">
+        <v>3.6</v>
+      </c>
+      <c r="L4">
+        <v>1.56</v>
+      </c>
+      <c r="M4">
         <v>1.1</v>
       </c>
-      <c r="H4">
-        <v>16.5</v>
-      </c>
-      <c r="I4">
-        <v>1000</v>
-      </c>
-      <c r="J4">
-        <v>11</v>
-      </c>
-      <c r="K4">
-        <v>32</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S4">
         <v>3.8</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="W4">
+        <v>1.56</v>
+      </c>
+      <c r="X4">
+        <v>11.5</v>
+      </c>
+      <c r="Y4">
+        <v>11.5</v>
+      </c>
+      <c r="Z4">
+        <v>17.5</v>
+      </c>
+      <c r="AA4">
+        <v>46</v>
+      </c>
+      <c r="AB4">
         <v>11</v>
       </c>
-      <c r="X4">
-        <v>1000</v>
-      </c>
-      <c r="Y4">
-        <v>1000</v>
-      </c>
-      <c r="Z4">
-        <v>1000</v>
-      </c>
-      <c r="AA4">
-        <v>1000</v>
-      </c>
-      <c r="AB4">
-        <v>1000</v>
-      </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG4">
-        <v>1.26</v>
+        <v>13</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR4">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="AT4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU4">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="AX4">
-        <v>4.9</v>
+        <v>15.5</v>
       </c>
       <c r="AY4">
-        <v>1.1</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>7.4</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>4.9</v>
+        <v>40</v>
       </c>
       <c r="BB4">
-        <v>4.9</v>
+        <v>38</v>
       </c>
       <c r="BC4">
-        <v>4.8</v>
+        <v>29</v>
       </c>
       <c r="BD4">
-        <v>4.9</v>
+        <v>40</v>
       </c>
       <c r="BE4">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="BF4">
-        <v>4.9</v>
+        <v>26</v>
       </c>
       <c r="BG4">
-        <v>4.9</v>
+        <v>23</v>
       </c>
       <c r="BH4" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:60">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
         <v>67</v>
       </c>
       <c r="D5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5">
+        <v>1.08</v>
+      </c>
+      <c r="G5">
+        <v>1.09</v>
+      </c>
+      <c r="H5">
+        <v>55</v>
+      </c>
+      <c r="I5">
         <v>75</v>
       </c>
-      <c r="E5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F5">
-        <v>1.01</v>
-      </c>
-      <c r="G5">
-        <v>1.01</v>
-      </c>
-      <c r="H5">
-        <v>50</v>
-      </c>
-      <c r="I5">
-        <v>1000</v>
-      </c>
       <c r="J5">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="K5">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1422,28 +1389,28 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V5">
         <v>1.01</v>
       </c>
       <c r="W5">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1470,1001 +1437,273 @@
         <v>1000</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AK5">
-        <v>1.39</v>
+        <v>8</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AM5">
         <v>1000</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="AO5">
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AQ5">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AR5">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AS5">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AT5">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AU5">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AV5">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AW5">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AX5">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="AY5">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="AZ5">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="BA5">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="BB5">
-        <v>11</v>
+        <v>5.4</v>
       </c>
       <c r="BC5">
-        <v>1.27</v>
+        <v>7</v>
       </c>
       <c r="BD5">
-        <v>3.55</v>
+        <v>19</v>
       </c>
       <c r="BE5">
-        <v>3.55</v>
+        <v>70</v>
       </c>
       <c r="BF5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BG5">
-        <v>3.6</v>
+        <v>160</v>
       </c>
       <c r="BH5" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:60">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>170</v>
+        <v>5.3</v>
       </c>
       <c r="H6">
-        <v>1.17</v>
+        <v>1.86</v>
       </c>
       <c r="I6">
-        <v>1.21</v>
+        <v>1.91</v>
       </c>
       <c r="J6">
-        <v>5.9</v>
+        <v>3.55</v>
       </c>
       <c r="K6">
-        <v>7.4</v>
+        <v>3.75</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R6">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S6">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V6">
-        <v>5.5</v>
+        <v>2.08</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE6">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH6">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="AI6">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL6">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO6">
-        <v>230</v>
+        <v>15</v>
       </c>
       <c r="AP6">
         <v>11</v>
       </c>
       <c r="AQ6">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="AR6">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AT6">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AU6">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AV6">
-        <v>1.39</v>
+        <v>9.4</v>
       </c>
       <c r="AW6">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="AX6">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AY6">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AZ6">
-        <v>5.7</v>
+        <v>18</v>
       </c>
       <c r="BA6">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BB6">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="BC6">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="BD6">
-        <v>8.6</v>
+        <v>48</v>
       </c>
       <c r="BE6">
-        <v>5.3</v>
+        <v>65</v>
       </c>
       <c r="BF6">
-        <v>5.3</v>
+        <v>55</v>
       </c>
       <c r="BG6">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BH6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:60">
-      <c r="A7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F7">
-        <v>1.78</v>
-      </c>
-      <c r="G7">
-        <v>1.85</v>
-      </c>
-      <c r="H7">
-        <v>4.4</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>4.6</v>
-      </c>
-      <c r="L7">
-        <v>1.31</v>
-      </c>
-      <c r="M7">
-        <v>1.04</v>
-      </c>
-      <c r="N7">
-        <v>5.2</v>
-      </c>
-      <c r="O7">
-        <v>1.21</v>
-      </c>
-      <c r="P7">
-        <v>2.42</v>
-      </c>
-      <c r="Q7">
-        <v>1.65</v>
-      </c>
-      <c r="R7">
-        <v>1.57</v>
-      </c>
-      <c r="S7">
-        <v>2.62</v>
-      </c>
-      <c r="T7">
-        <v>1.65</v>
-      </c>
-      <c r="U7">
-        <v>2.32</v>
-      </c>
-      <c r="V7">
-        <v>1.25</v>
-      </c>
-      <c r="W7">
-        <v>2.16</v>
-      </c>
-      <c r="X7">
-        <v>23</v>
-      </c>
-      <c r="Y7">
-        <v>24</v>
-      </c>
-      <c r="Z7">
-        <v>46</v>
-      </c>
-      <c r="AA7">
-        <v>120</v>
-      </c>
-      <c r="AB7">
-        <v>12.5</v>
-      </c>
-      <c r="AC7">
-        <v>10.5</v>
-      </c>
-      <c r="AD7">
-        <v>19</v>
-      </c>
-      <c r="AE7">
-        <v>55</v>
-      </c>
-      <c r="AF7">
-        <v>13</v>
-      </c>
-      <c r="AG7">
-        <v>11</v>
-      </c>
-      <c r="AH7">
-        <v>17.5</v>
-      </c>
-      <c r="AI7">
-        <v>70</v>
-      </c>
-      <c r="AJ7">
-        <v>20</v>
-      </c>
-      <c r="AK7">
-        <v>17.5</v>
-      </c>
-      <c r="AL7">
-        <v>32</v>
-      </c>
-      <c r="AM7">
-        <v>95</v>
-      </c>
-      <c r="AN7">
-        <v>8.4</v>
-      </c>
-      <c r="AO7">
-        <v>75</v>
-      </c>
-      <c r="AP7">
-        <v>20</v>
-      </c>
-      <c r="AQ7">
-        <v>18.5</v>
-      </c>
-      <c r="AR7">
-        <v>30</v>
-      </c>
-      <c r="AS7">
-        <v>60</v>
-      </c>
-      <c r="AT7">
-        <v>10</v>
-      </c>
-      <c r="AU7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV7">
-        <v>16</v>
-      </c>
-      <c r="AW7">
-        <v>36</v>
-      </c>
-      <c r="AX7">
-        <v>11</v>
-      </c>
-      <c r="AY7">
-        <v>9</v>
-      </c>
-      <c r="AZ7">
-        <v>15</v>
-      </c>
-      <c r="BA7">
-        <v>34</v>
-      </c>
-      <c r="BB7">
-        <v>16.5</v>
-      </c>
-      <c r="BC7">
-        <v>14.5</v>
-      </c>
-      <c r="BD7">
-        <v>22</v>
-      </c>
-      <c r="BE7">
-        <v>55</v>
-      </c>
-      <c r="BF7">
-        <v>7.2</v>
-      </c>
-      <c r="BG7">
-        <v>25</v>
-      </c>
-      <c r="BH7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:60">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8">
-        <v>2.9</v>
-      </c>
-      <c r="G8">
-        <v>2.92</v>
-      </c>
-      <c r="H8">
-        <v>2.7</v>
-      </c>
-      <c r="I8">
-        <v>2.72</v>
-      </c>
-      <c r="J8">
-        <v>3.4</v>
-      </c>
-      <c r="K8">
-        <v>3.55</v>
-      </c>
-      <c r="L8">
-        <v>1.39</v>
-      </c>
-      <c r="M8">
-        <v>1.06</v>
-      </c>
-      <c r="N8">
-        <v>4.3</v>
-      </c>
-      <c r="O8">
-        <v>1.28</v>
-      </c>
-      <c r="P8">
-        <v>2.1</v>
-      </c>
-      <c r="Q8">
-        <v>1.86</v>
-      </c>
-      <c r="R8">
-        <v>1.43</v>
-      </c>
-      <c r="S8">
-        <v>3.1</v>
-      </c>
-      <c r="T8">
-        <v>1.69</v>
-      </c>
-      <c r="U8">
-        <v>2.34</v>
-      </c>
-      <c r="V8">
-        <v>1.58</v>
-      </c>
-      <c r="W8">
-        <v>1.52</v>
-      </c>
-      <c r="X8">
-        <v>16</v>
-      </c>
-      <c r="Y8">
-        <v>13</v>
-      </c>
-      <c r="Z8">
-        <v>18.5</v>
-      </c>
-      <c r="AA8">
-        <v>46</v>
-      </c>
-      <c r="AB8">
-        <v>13.5</v>
-      </c>
-      <c r="AC8">
-        <v>8</v>
-      </c>
-      <c r="AD8">
-        <v>12.5</v>
-      </c>
-      <c r="AE8">
-        <v>27</v>
-      </c>
-      <c r="AF8">
-        <v>21</v>
-      </c>
-      <c r="AG8">
-        <v>12.5</v>
-      </c>
-      <c r="AH8">
-        <v>15</v>
-      </c>
-      <c r="AI8">
-        <v>36</v>
-      </c>
-      <c r="AJ8">
-        <v>44</v>
-      </c>
-      <c r="AK8">
-        <v>29</v>
-      </c>
-      <c r="AL8">
-        <v>40</v>
-      </c>
-      <c r="AM8">
-        <v>85</v>
-      </c>
-      <c r="AN8">
-        <v>24</v>
-      </c>
-      <c r="AO8">
-        <v>21</v>
-      </c>
-      <c r="AP8">
-        <v>14.5</v>
-      </c>
-      <c r="AQ8">
-        <v>11.5</v>
-      </c>
-      <c r="AR8">
-        <v>16.5</v>
-      </c>
-      <c r="AS8">
-        <v>34</v>
-      </c>
-      <c r="AT8">
-        <v>12</v>
-      </c>
-      <c r="AU8">
-        <v>7.4</v>
-      </c>
-      <c r="AV8">
-        <v>11</v>
-      </c>
-      <c r="AW8">
-        <v>24</v>
-      </c>
-      <c r="AX8">
-        <v>18.5</v>
-      </c>
-      <c r="AY8">
-        <v>11.5</v>
-      </c>
-      <c r="AZ8">
-        <v>14</v>
-      </c>
-      <c r="BA8">
-        <v>32</v>
-      </c>
-      <c r="BB8">
-        <v>38</v>
-      </c>
-      <c r="BC8">
-        <v>26</v>
-      </c>
-      <c r="BD8">
-        <v>16.5</v>
-      </c>
-      <c r="BE8">
-        <v>70</v>
-      </c>
-      <c r="BF8">
-        <v>21</v>
-      </c>
-      <c r="BG8">
-        <v>18.5</v>
-      </c>
-      <c r="BH8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:60">
-      <c r="A9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" t="s">
         <v>79</v>
-      </c>
-      <c r="E9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F9">
-        <v>2.7</v>
-      </c>
-      <c r="G9">
-        <v>2.78</v>
-      </c>
-      <c r="H9">
-        <v>2.8</v>
-      </c>
-      <c r="I9">
-        <v>2.86</v>
-      </c>
-      <c r="J9">
-        <v>3.55</v>
-      </c>
-      <c r="K9">
-        <v>3.65</v>
-      </c>
-      <c r="L9">
-        <v>1.37</v>
-      </c>
-      <c r="M9">
-        <v>1.06</v>
-      </c>
-      <c r="N9">
-        <v>4.4</v>
-      </c>
-      <c r="O9">
-        <v>1.27</v>
-      </c>
-      <c r="P9">
-        <v>2.14</v>
-      </c>
-      <c r="Q9">
-        <v>1.83</v>
-      </c>
-      <c r="R9">
-        <v>1.45</v>
-      </c>
-      <c r="S9">
-        <v>3.05</v>
-      </c>
-      <c r="T9">
-        <v>1.68</v>
-      </c>
-      <c r="U9">
-        <v>2.4</v>
-      </c>
-      <c r="V9">
-        <v>1.54</v>
-      </c>
-      <c r="W9">
-        <v>1.56</v>
-      </c>
-      <c r="X9">
-        <v>17</v>
-      </c>
-      <c r="Y9">
-        <v>13.5</v>
-      </c>
-      <c r="Z9">
-        <v>20</v>
-      </c>
-      <c r="AA9">
-        <v>42</v>
-      </c>
-      <c r="AB9">
-        <v>13.5</v>
-      </c>
-      <c r="AC9">
-        <v>8</v>
-      </c>
-      <c r="AD9">
-        <v>12.5</v>
-      </c>
-      <c r="AE9">
-        <v>28</v>
-      </c>
-      <c r="AF9">
-        <v>19.5</v>
-      </c>
-      <c r="AG9">
-        <v>12.5</v>
-      </c>
-      <c r="AH9">
-        <v>16</v>
-      </c>
-      <c r="AI9">
-        <v>38</v>
-      </c>
-      <c r="AJ9">
-        <v>42</v>
-      </c>
-      <c r="AK9">
-        <v>28</v>
-      </c>
-      <c r="AL9">
-        <v>38</v>
-      </c>
-      <c r="AM9">
-        <v>75</v>
-      </c>
-      <c r="AN9">
-        <v>20</v>
-      </c>
-      <c r="AO9">
-        <v>22</v>
-      </c>
-      <c r="AP9">
-        <v>15</v>
-      </c>
-      <c r="AQ9">
-        <v>12</v>
-      </c>
-      <c r="AR9">
-        <v>18</v>
-      </c>
-      <c r="AS9">
-        <v>32</v>
-      </c>
-      <c r="AT9">
-        <v>12</v>
-      </c>
-      <c r="AU9">
-        <v>7.4</v>
-      </c>
-      <c r="AV9">
-        <v>11</v>
-      </c>
-      <c r="AW9">
-        <v>23</v>
-      </c>
-      <c r="AX9">
-        <v>17</v>
-      </c>
-      <c r="AY9">
-        <v>11</v>
-      </c>
-      <c r="AZ9">
-        <v>13.5</v>
-      </c>
-      <c r="BA9">
-        <v>30</v>
-      </c>
-      <c r="BB9">
-        <v>34</v>
-      </c>
-      <c r="BC9">
-        <v>24</v>
-      </c>
-      <c r="BD9">
-        <v>32</v>
-      </c>
-      <c r="BE9">
-        <v>14</v>
-      </c>
-      <c r="BF9">
-        <v>18</v>
-      </c>
-      <c r="BG9">
-        <v>19</v>
-      </c>
-      <c r="BH9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:60">
-      <c r="A10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" t="s">
-        <v>89</v>
-      </c>
-      <c r="F10">
-        <v>4.7</v>
-      </c>
-      <c r="G10">
-        <v>5.2</v>
-      </c>
-      <c r="H10">
-        <v>1.89</v>
-      </c>
-      <c r="I10">
-        <v>1.96</v>
-      </c>
-      <c r="J10">
-        <v>3.55</v>
-      </c>
-      <c r="K10">
-        <v>3.8</v>
-      </c>
-      <c r="L10">
-        <v>1.45</v>
-      </c>
-      <c r="M10">
-        <v>1.08</v>
-      </c>
-      <c r="N10">
-        <v>3.6</v>
-      </c>
-      <c r="O10">
-        <v>1.36</v>
-      </c>
-      <c r="P10">
-        <v>1.85</v>
-      </c>
-      <c r="Q10">
-        <v>2.08</v>
-      </c>
-      <c r="R10">
-        <v>1.32</v>
-      </c>
-      <c r="S10">
-        <v>3.85</v>
-      </c>
-      <c r="T10">
-        <v>1.87</v>
-      </c>
-      <c r="U10">
-        <v>2</v>
-      </c>
-      <c r="V10">
-        <v>2.04</v>
-      </c>
-      <c r="W10">
-        <v>1.24</v>
-      </c>
-      <c r="X10">
-        <v>14</v>
-      </c>
-      <c r="Y10">
-        <v>8.4</v>
-      </c>
-      <c r="Z10">
-        <v>11.5</v>
-      </c>
-      <c r="AA10">
-        <v>22</v>
-      </c>
-      <c r="AB10">
-        <v>16.5</v>
-      </c>
-      <c r="AC10">
-        <v>8.6</v>
-      </c>
-      <c r="AD10">
-        <v>10.5</v>
-      </c>
-      <c r="AE10">
-        <v>22</v>
-      </c>
-      <c r="AF10">
-        <v>38</v>
-      </c>
-      <c r="AG10">
-        <v>21</v>
-      </c>
-      <c r="AH10">
-        <v>21</v>
-      </c>
-      <c r="AI10">
-        <v>40</v>
-      </c>
-      <c r="AJ10">
-        <v>140</v>
-      </c>
-      <c r="AK10">
-        <v>70</v>
-      </c>
-      <c r="AL10">
-        <v>130</v>
-      </c>
-      <c r="AM10">
-        <v>130</v>
-      </c>
-      <c r="AN10">
-        <v>90</v>
-      </c>
-      <c r="AO10">
-        <v>15.5</v>
-      </c>
-      <c r="AP10">
-        <v>10.5</v>
-      </c>
-      <c r="AQ10">
-        <v>7.6</v>
-      </c>
-      <c r="AR10">
-        <v>9.6</v>
-      </c>
-      <c r="AS10">
-        <v>18.5</v>
-      </c>
-      <c r="AT10">
-        <v>13</v>
-      </c>
-      <c r="AU10">
-        <v>7</v>
-      </c>
-      <c r="AV10">
-        <v>9</v>
-      </c>
-      <c r="AW10">
-        <v>19</v>
-      </c>
-      <c r="AX10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY10">
-        <v>16</v>
-      </c>
-      <c r="AZ10">
-        <v>17</v>
-      </c>
-      <c r="BA10">
-        <v>8.4</v>
-      </c>
-      <c r="BB10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD10">
-        <v>24</v>
-      </c>
-      <c r="BE10">
-        <v>9.6</v>
-      </c>
-      <c r="BF10">
-        <v>9.4</v>
-      </c>
-      <c r="BG10">
-        <v>12.5</v>
-      </c>
-      <c r="BH10" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
